--- a/法诉案件导入_问题明细.xlsx
+++ b/法诉案件导入_问题明细.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题明细" sheetId="1" r:id="Rfd7ca3301cb14b81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R6509f346d709423d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题明细" sheetId="1" r:id="Ra0f197927dd74a51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R9f4aab17190644ba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -127,9 +127,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -142,12 +142,58 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="dk1"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="accent1"/>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
+                <a:satMod val="110000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="12700">
@@ -241,15 +287,11 @@
     <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="8" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="12" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="8" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="12" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="8" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="8" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="8" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="40" customHeight="1">
@@ -269,40 +311,28 @@
         <x:v>客户姓名</x:v>
       </x:c>
       <x:c r="F1" s="8" t="str">
-        <x:v>处理环节</x:v>
+        <x:v>导入结果</x:v>
       </x:c>
       <x:c r="G1" s="8" t="str">
-        <x:v>导入结果</x:v>
+        <x:v>问题类型</x:v>
       </x:c>
       <x:c r="H1" s="8" t="str">
-        <x:v>问题类型</x:v>
+        <x:v>字段路径</x:v>
       </x:c>
       <x:c r="I1" s="8" t="str">
-        <x:v>字段路径</x:v>
+        <x:v>当前值</x:v>
       </x:c>
       <x:c r="J1" s="8" t="str">
-        <x:v>当前值</x:v>
+        <x:v>问题说明</x:v>
       </x:c>
       <x:c r="K1" s="8" t="str">
-        <x:v>问题说明</x:v>
+        <x:v>是否阻断导入</x:v>
       </x:c>
       <x:c r="L1" s="8" t="str">
-        <x:v>建议处理</x:v>
+        <x:v>材料项</x:v>
       </x:c>
       <x:c r="M1" s="8" t="str">
-        <x:v>是否阻断导入</x:v>
-      </x:c>
-      <x:c r="N1" s="8" t="str">
-        <x:v>材料项</x:v>
-      </x:c>
-      <x:c r="O1" s="8" t="str">
         <x:v>导入时间</x:v>
-      </x:c>
-      <x:c r="P1" s="8" t="str">
-        <x:v>处理状态</x:v>
-      </x:c>
-      <x:c r="Q1" s="8" t="str">
-        <x:v>备注</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -322,38 +352,26 @@
         <x:v>张三</x:v>
       </x:c>
       <x:c r="F2" s="9" t="str">
-        <x:v>资产明细检查</x:v>
+        <x:v>重复待确认</x:v>
       </x:c>
       <x:c r="G2" s="9" t="str">
-        <x:v>阻断失败</x:v>
+        <x:v>重复待确认</x:v>
       </x:c>
       <x:c r="H2" s="9" t="str">
-        <x:v>账单期次重复</x:v>
+        <x:v>订单基础信息-订单编号</x:v>
       </x:c>
       <x:c r="I2" s="9" t="str">
-        <x:v>账单信息-期次</x:v>
+        <x:v>26012915050167612327</x:v>
       </x:c>
       <x:c r="J2" s="9" t="str">
-        <x:v>第3期重复</x:v>
+        <x:v>系统已存在同外部资产方、同订单编号案件，本次不新增案件、不自动覆盖字段和材料</x:v>
       </x:c>
       <x:c r="K2" s="9" t="str">
-        <x:v>同一订单第3期出现2次</x:v>
-      </x:c>
-      <x:c r="L2" s="9" t="str">
-        <x:v>修改模板后重新上传</x:v>
-      </x:c>
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L2" s="9" t="str"/>
       <x:c r="M2" s="9" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="N2" s="9" t="str"/>
-      <x:c r="O2" s="9" t="str">
         <x:v>2026-06-10 20:15:32</x:v>
-      </x:c>
-      <x:c r="P2" s="9" t="str">
-        <x:v>待处理</x:v>
-      </x:c>
-      <x:c r="Q2" s="9" t="str">
-        <x:v>示例数据</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -373,38 +391,26 @@
         <x:v>黄丽</x:v>
       </x:c>
       <x:c r="F3" s="9" t="str">
-        <x:v>材料检查</x:v>
+        <x:v>新增成功</x:v>
       </x:c>
       <x:c r="G3" s="9" t="str">
-        <x:v>导入成功</x:v>
+        <x:v>必传合同缺失</x:v>
       </x:c>
       <x:c r="H3" s="9" t="str">
-        <x:v>必传合同缺失</x:v>
-      </x:c>
-      <x:c r="I3" s="9" t="str">
         <x:v>文件信息-电子签章授权书</x:v>
       </x:c>
-      <x:c r="J3" s="9" t="str"/>
+      <x:c r="I3" s="9" t="str"/>
+      <x:c r="J3" s="9" t="str">
+        <x:v>电子签章授权书未上传，案件为未生效状态</x:v>
+      </x:c>
       <x:c r="K3" s="9" t="str">
-        <x:v>电子签章授权书未上传</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="L3" s="9" t="str">
-        <x:v>进入材料补传页补齐必传合同</x:v>
+        <x:v>电子签章授权书</x:v>
       </x:c>
       <x:c r="M3" s="9" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="N3" s="9" t="str">
-        <x:v>电子签章授权书</x:v>
-      </x:c>
-      <x:c r="O3" s="9" t="str">
         <x:v>2026-06-10 20:15:32</x:v>
-      </x:c>
-      <x:c r="P3" s="9" t="str">
-        <x:v>待补传</x:v>
-      </x:c>
-      <x:c r="Q3" s="9" t="str">
-        <x:v>示例数据</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -424,36 +430,24 @@
         <x:v>李明</x:v>
       </x:c>
       <x:c r="F4" s="9" t="str">
-        <x:v>订单关系检查</x:v>
+        <x:v>导入失败</x:v>
       </x:c>
       <x:c r="G4" s="9" t="str">
-        <x:v>阻断失败</x:v>
+        <x:v>主续关系异常</x:v>
       </x:c>
       <x:c r="H4" s="9" t="str">
-        <x:v>主续关系异常</x:v>
-      </x:c>
-      <x:c r="I4" s="9" t="str">
         <x:v>订单基础信息-父订单编号</x:v>
       </x:c>
-      <x:c r="J4" s="9" t="str"/>
+      <x:c r="I4" s="9" t="str"/>
+      <x:c r="J4" s="9" t="str">
+        <x:v>续租订单未匹配到首租订单</x:v>
+      </x:c>
       <x:c r="K4" s="9" t="str">
-        <x:v>续租订单未匹配到首租订单</x:v>
-      </x:c>
-      <x:c r="L4" s="9" t="str">
-        <x:v>补充首租订单或确认系统内已存在首租订单</x:v>
-      </x:c>
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="L4" s="9" t="str"/>
       <x:c r="M4" s="9" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="N4" s="9" t="str"/>
-      <x:c r="O4" s="9" t="str">
         <x:v>2026-06-10 20:15:32</x:v>
-      </x:c>
-      <x:c r="P4" s="9" t="str">
-        <x:v>待处理</x:v>
-      </x:c>
-      <x:c r="Q4" s="9" t="str">
-        <x:v>示例数据</x:v>
       </x:c>
     </x:row>
     <x:row r="5">

--- a/法诉案件导入_问题明细.xlsx
+++ b/法诉案件导入_问题明细.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题明细" sheetId="1" r:id="Ra0f197927dd74a51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R9f4aab17190644ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题明细" sheetId="1" r:id="Rf9821866f38e4c53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="Re057de3674d847e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -287,11 +287,10 @@
     <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="8" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="8" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="8" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="40" customHeight="1">
@@ -320,18 +319,15 @@
         <x:v>字段路径</x:v>
       </x:c>
       <x:c r="I1" s="8" t="str">
-        <x:v>当前值</x:v>
+        <x:v>问题说明</x:v>
       </x:c>
       <x:c r="J1" s="8" t="str">
-        <x:v>问题说明</x:v>
+        <x:v>是否阻断导入</x:v>
       </x:c>
       <x:c r="K1" s="8" t="str">
-        <x:v>是否阻断导入</x:v>
+        <x:v>材料项</x:v>
       </x:c>
       <x:c r="L1" s="8" t="str">
-        <x:v>材料项</x:v>
-      </x:c>
-      <x:c r="M1" s="8" t="str">
         <x:v>导入时间</x:v>
       </x:c>
     </x:row>
@@ -361,16 +357,13 @@
         <x:v>订单基础信息-订单编号</x:v>
       </x:c>
       <x:c r="I2" s="9" t="str">
-        <x:v>26012915050167612327</x:v>
+        <x:v>系统已存在同外部资产方、同订单编号案件，本次不新增案件、不自动覆盖字段和材料</x:v>
       </x:c>
       <x:c r="J2" s="9" t="str">
-        <x:v>系统已存在同外部资产方、同订单编号案件，本次不新增案件、不自动覆盖字段和材料</x:v>
-      </x:c>
-      <x:c r="K2" s="9" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="L2" s="9" t="str"/>
-      <x:c r="M2" s="9" t="str">
+      <x:c r="K2" s="9" t="str"/>
+      <x:c r="L2" s="9" t="str">
         <x:v>2026-06-10 20:15:32</x:v>
       </x:c>
     </x:row>
@@ -399,17 +392,16 @@
       <x:c r="H3" s="9" t="str">
         <x:v>文件信息-电子签章授权书</x:v>
       </x:c>
-      <x:c r="I3" s="9" t="str"/>
+      <x:c r="I3" s="9" t="str">
+        <x:v>电子签章授权书未上传，案件为未生效状态</x:v>
+      </x:c>
       <x:c r="J3" s="9" t="str">
-        <x:v>电子签章授权书未上传，案件为未生效状态</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="K3" s="9" t="str">
-        <x:v>否</x:v>
+        <x:v>电子签章授权书</x:v>
       </x:c>
       <x:c r="L3" s="9" t="str">
-        <x:v>电子签章授权书</x:v>
-      </x:c>
-      <x:c r="M3" s="9" t="str">
         <x:v>2026-06-10 20:15:32</x:v>
       </x:c>
     </x:row>
@@ -438,15 +430,14 @@
       <x:c r="H4" s="9" t="str">
         <x:v>订单基础信息-父订单编号</x:v>
       </x:c>
-      <x:c r="I4" s="9" t="str"/>
+      <x:c r="I4" s="9" t="str">
+        <x:v>续租订单未匹配到首租订单</x:v>
+      </x:c>
       <x:c r="J4" s="9" t="str">
-        <x:v>续租订单未匹配到首租订单</x:v>
-      </x:c>
-      <x:c r="K4" s="9" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="L4" s="9" t="str"/>
-      <x:c r="M4" s="9" t="str">
+      <x:c r="K4" s="9" t="str"/>
+      <x:c r="L4" s="9" t="str">
         <x:v>2026-06-10 20:15:32</x:v>
       </x:c>
     </x:row>

--- a/法诉案件导入_问题明细.xlsx
+++ b/法诉案件导入_问题明细.xlsx
@@ -2,8 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题明细" sheetId="1" r:id="Rf9821866f38e4c53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="Re057de3674d847e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="Rd7a594442a764abb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,8 +13,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="200" formatCode="@"/>
+    <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
   </x:numFmts>
   <x:fonts count="4">
     <x:font>
@@ -57,7 +57,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="11">
+  <x:cellXfs count="12">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -77,6 +77,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -280,7 +281,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
@@ -288,9 +289,11 @@
     <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="8" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="12" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="40" customHeight="1">
@@ -310,24 +313,30 @@
         <x:v>客户姓名</x:v>
       </x:c>
       <x:c r="F1" s="8" t="str">
+        <x:v>业务类型</x:v>
+      </x:c>
+      <x:c r="G1" s="8" t="str">
+        <x:v>主续订单</x:v>
+      </x:c>
+      <x:c r="H1" s="8" t="str">
+        <x:v>债权金额</x:v>
+      </x:c>
+      <x:c r="I1" s="8" t="str">
+        <x:v>逾期天数</x:v>
+      </x:c>
+      <x:c r="J1" s="8" t="str">
         <x:v>导入结果</x:v>
       </x:c>
-      <x:c r="G1" s="8" t="str">
-        <x:v>问题类型</x:v>
-      </x:c>
-      <x:c r="H1" s="8" t="str">
-        <x:v>字段路径</x:v>
-      </x:c>
-      <x:c r="I1" s="8" t="str">
-        <x:v>问题说明</x:v>
-      </x:c>
-      <x:c r="J1" s="8" t="str">
-        <x:v>是否阻断导入</x:v>
-      </x:c>
       <x:c r="K1" s="8" t="str">
-        <x:v>材料项</x:v>
+        <x:v>材料状态</x:v>
       </x:c>
       <x:c r="L1" s="8" t="str">
+        <x:v>失败原因</x:v>
+      </x:c>
+      <x:c r="M1" s="8" t="str">
+        <x:v>处理建议</x:v>
+      </x:c>
+      <x:c r="N1" s="8" t="str">
         <x:v>导入时间</x:v>
       </x:c>
     </x:row>
@@ -348,22 +357,28 @@
         <x:v>张三</x:v>
       </x:c>
       <x:c r="F2" s="9" t="str">
-        <x:v>重复待确认</x:v>
+        <x:v>租赁</x:v>
       </x:c>
       <x:c r="G2" s="9" t="str">
-        <x:v>重复待确认</x:v>
-      </x:c>
-      <x:c r="H2" s="9" t="str">
-        <x:v>订单基础信息-订单编号</x:v>
-      </x:c>
-      <x:c r="I2" s="9" t="str">
-        <x:v>系统已存在同外部资产方、同订单编号案件，本次不新增案件、不自动覆盖字段和材料</x:v>
+        <x:v>主订单</x:v>
+      </x:c>
+      <x:c r="H2" s="11" t="n">
+        <x:v>12036.8</x:v>
+      </x:c>
+      <x:c r="I2" s="9" t="n">
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J2" s="9" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="K2" s="9" t="str"/>
-      <x:c r="L2" s="9" t="str">
+        <x:v>导入成功</x:v>
+      </x:c>
+      <x:c r="K2" s="9" t="str">
+        <x:v>完整</x:v>
+      </x:c>
+      <x:c r="L2" s="9" t="str"/>
+      <x:c r="M2" s="9" t="str">
+        <x:v>已进入原待委外链路</x:v>
+      </x:c>
+      <x:c r="N2" s="9" t="str">
         <x:v>2026-06-10 20:15:32</x:v>
       </x:c>
     </x:row>
@@ -384,24 +399,30 @@
         <x:v>黄丽</x:v>
       </x:c>
       <x:c r="F3" s="9" t="str">
-        <x:v>新增成功</x:v>
+        <x:v>租赁</x:v>
       </x:c>
       <x:c r="G3" s="9" t="str">
-        <x:v>必传合同缺失</x:v>
-      </x:c>
-      <x:c r="H3" s="9" t="str">
-        <x:v>文件信息-电子签章授权书</x:v>
-      </x:c>
-      <x:c r="I3" s="9" t="str">
-        <x:v>电子签章授权书未上传，案件为未生效状态</x:v>
+        <x:v>续租订单</x:v>
+      </x:c>
+      <x:c r="H3" s="11" t="n">
+        <x:v>9420</x:v>
+      </x:c>
+      <x:c r="I3" s="9" t="n">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J3" s="9" t="str">
-        <x:v>否</x:v>
+        <x:v>导入成功</x:v>
       </x:c>
       <x:c r="K3" s="9" t="str">
-        <x:v>电子签章授权书</x:v>
+        <x:v>材料待处理</x:v>
       </x:c>
       <x:c r="L3" s="9" t="str">
+        <x:v>电子签章授权书未上传</x:v>
+      </x:c>
+      <x:c r="M3" s="9" t="str">
+        <x:v>进入材料补传页补齐必传合同</x:v>
+      </x:c>
+      <x:c r="N3" s="9" t="str">
         <x:v>2026-06-10 20:15:32</x:v>
       </x:c>
     </x:row>
@@ -422,4087 +443,5094 @@
         <x:v>李明</x:v>
       </x:c>
       <x:c r="F4" s="9" t="str">
-        <x:v>导入失败</x:v>
+        <x:v>租赁</x:v>
       </x:c>
       <x:c r="G4" s="9" t="str">
-        <x:v>主续关系异常</x:v>
-      </x:c>
-      <x:c r="H4" s="9" t="str">
-        <x:v>订单基础信息-父订单编号</x:v>
-      </x:c>
-      <x:c r="I4" s="9" t="str">
-        <x:v>续租订单未匹配到首租订单</x:v>
+        <x:v>续租订单</x:v>
+      </x:c>
+      <x:c r="H4" s="11" t="n">
+        <x:v>7290</x:v>
+      </x:c>
+      <x:c r="I4" s="9" t="n">
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J4" s="9" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="K4" s="9" t="str"/>
+        <x:v>阻断失败</x:v>
+      </x:c>
+      <x:c r="K4" s="9" t="str">
+        <x:v>未上传</x:v>
+      </x:c>
       <x:c r="L4" s="9" t="str">
+        <x:v>续租订单未匹配到首租订单；合同附件未上传</x:v>
+      </x:c>
+      <x:c r="M4" s="9" t="str">
+        <x:v>补充首租订单或确认系统内已有首租订单，并补传合同附件</x:v>
+      </x:c>
+      <x:c r="N4" s="9" t="str">
         <x:v>2026-06-10 20:15:32</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="B5" s="10"/>
-      <x:c r="D5" s="10"/>
+      <x:c r="A5" t="str">
+        <x:v>创新</x:v>
+      </x:c>
+      <x:c r="B5" s="10" t="str">
+        <x:v>DR202606100001</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>创新租赁旧合同批次01</x:v>
+      </x:c>
+      <x:c r="D5" s="10" t="str">
+        <x:v>26012915050167612331</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>周强</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>租赁</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>主订单</x:v>
+      </x:c>
+      <x:c r="H5" s="11" t="n">
+        <x:v>8650</x:v>
+      </x:c>
+      <x:c r="I5" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J5" t="str">
+        <x:v>阻断失败</x:v>
+      </x:c>
+      <x:c r="K5" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L5" t="str">
+        <x:v>重复导入：该订单已在批次DR202606080003（创新租赁旧合同批次00）导入落库；同一批资产多次导入时，以首次导入数据为准，本批次不能重复导入或自动覆盖。</x:v>
+      </x:c>
+      <x:c r="M5" t="str">
+        <x:v>请到首次导入批次DR202606080003查看该订单；如需更正，按原批次处理或走批量补传/更正流程。</x:v>
+      </x:c>
+      <x:c r="N5" t="str">
+        <x:v>2026-06-10 20:15:32</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="B6" s="10"/>
       <x:c r="D6" s="10"/>
+      <x:c r="H6" s="11"/>
     </x:row>
     <x:row r="7">
       <x:c r="B7" s="10"/>
       <x:c r="D7" s="10"/>
+      <x:c r="H7" s="11"/>
     </x:row>
     <x:row r="8">
       <x:c r="B8" s="10"/>
       <x:c r="D8" s="10"/>
+      <x:c r="H8" s="11"/>
     </x:row>
     <x:row r="9">
       <x:c r="B9" s="10"/>
       <x:c r="D9" s="10"/>
+      <x:c r="H9" s="11"/>
     </x:row>
     <x:row r="10">
       <x:c r="B10" s="10"/>
       <x:c r="D10" s="10"/>
+      <x:c r="H10" s="11"/>
     </x:row>
     <x:row r="11">
       <x:c r="B11" s="10"/>
       <x:c r="D11" s="10"/>
+      <x:c r="H11" s="11"/>
     </x:row>
     <x:row r="12">
       <x:c r="B12" s="10"/>
       <x:c r="D12" s="10"/>
+      <x:c r="H12" s="11"/>
     </x:row>
     <x:row r="13">
       <x:c r="B13" s="10"/>
       <x:c r="D13" s="10"/>
+      <x:c r="H13" s="11"/>
     </x:row>
     <x:row r="14">
       <x:c r="B14" s="10"/>
       <x:c r="D14" s="10"/>
+      <x:c r="H14" s="11"/>
     </x:row>
     <x:row r="15">
       <x:c r="B15" s="10"/>
       <x:c r="D15" s="10"/>
+      <x:c r="H15" s="11"/>
     </x:row>
     <x:row r="16">
       <x:c r="B16" s="10"/>
       <x:c r="D16" s="10"/>
+      <x:c r="H16" s="11"/>
     </x:row>
     <x:row r="17">
       <x:c r="B17" s="10"/>
       <x:c r="D17" s="10"/>
+      <x:c r="H17" s="11"/>
     </x:row>
     <x:row r="18">
       <x:c r="B18" s="10"/>
       <x:c r="D18" s="10"/>
+      <x:c r="H18" s="11"/>
     </x:row>
     <x:row r="19">
       <x:c r="B19" s="10"/>
       <x:c r="D19" s="10"/>
+      <x:c r="H19" s="11"/>
     </x:row>
     <x:row r="20">
       <x:c r="B20" s="10"/>
       <x:c r="D20" s="10"/>
+      <x:c r="H20" s="11"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="10"/>
       <x:c r="D21" s="10"/>
+      <x:c r="H21" s="11"/>
     </x:row>
     <x:row r="22">
       <x:c r="B22" s="10"/>
       <x:c r="D22" s="10"/>
+      <x:c r="H22" s="11"/>
     </x:row>
     <x:row r="23">
       <x:c r="B23" s="10"/>
       <x:c r="D23" s="10"/>
+      <x:c r="H23" s="11"/>
     </x:row>
     <x:row r="24">
       <x:c r="B24" s="10"/>
       <x:c r="D24" s="10"/>
+      <x:c r="H24" s="11"/>
     </x:row>
     <x:row r="25">
       <x:c r="B25" s="10"/>
       <x:c r="D25" s="10"/>
+      <x:c r="H25" s="11"/>
     </x:row>
     <x:row r="26">
       <x:c r="B26" s="10"/>
       <x:c r="D26" s="10"/>
+      <x:c r="H26" s="11"/>
     </x:row>
     <x:row r="27">
       <x:c r="B27" s="10"/>
       <x:c r="D27" s="10"/>
+      <x:c r="H27" s="11"/>
     </x:row>
     <x:row r="28">
       <x:c r="B28" s="10"/>
       <x:c r="D28" s="10"/>
+      <x:c r="H28" s="11"/>
     </x:row>
     <x:row r="29">
       <x:c r="B29" s="10"/>
       <x:c r="D29" s="10"/>
+      <x:c r="H29" s="11"/>
     </x:row>
     <x:row r="30">
       <x:c r="B30" s="10"/>
       <x:c r="D30" s="10"/>
+      <x:c r="H30" s="11"/>
     </x:row>
     <x:row r="31">
       <x:c r="B31" s="10"/>
       <x:c r="D31" s="10"/>
+      <x:c r="H31" s="11"/>
     </x:row>
     <x:row r="32">
       <x:c r="B32" s="10"/>
       <x:c r="D32" s="10"/>
+      <x:c r="H32" s="11"/>
     </x:row>
     <x:row r="33">
       <x:c r="B33" s="10"/>
       <x:c r="D33" s="10"/>
+      <x:c r="H33" s="11"/>
     </x:row>
     <x:row r="34">
       <x:c r="B34" s="10"/>
       <x:c r="D34" s="10"/>
+      <x:c r="H34" s="11"/>
     </x:row>
     <x:row r="35">
       <x:c r="B35" s="10"/>
       <x:c r="D35" s="10"/>
+      <x:c r="H35" s="11"/>
     </x:row>
     <x:row r="36">
       <x:c r="B36" s="10"/>
       <x:c r="D36" s="10"/>
+      <x:c r="H36" s="11"/>
     </x:row>
     <x:row r="37">
       <x:c r="B37" s="10"/>
       <x:c r="D37" s="10"/>
+      <x:c r="H37" s="11"/>
     </x:row>
     <x:row r="38">
       <x:c r="B38" s="10"/>
       <x:c r="D38" s="10"/>
+      <x:c r="H38" s="11"/>
     </x:row>
     <x:row r="39">
       <x:c r="B39" s="10"/>
       <x:c r="D39" s="10"/>
+      <x:c r="H39" s="11"/>
     </x:row>
     <x:row r="40">
       <x:c r="B40" s="10"/>
       <x:c r="D40" s="10"/>
+      <x:c r="H40" s="11"/>
     </x:row>
     <x:row r="41">
       <x:c r="B41" s="10"/>
       <x:c r="D41" s="10"/>
+      <x:c r="H41" s="11"/>
     </x:row>
     <x:row r="42">
       <x:c r="B42" s="10"/>
       <x:c r="D42" s="10"/>
+      <x:c r="H42" s="11"/>
     </x:row>
     <x:row r="43">
       <x:c r="B43" s="10"/>
       <x:c r="D43" s="10"/>
+      <x:c r="H43" s="11"/>
     </x:row>
     <x:row r="44">
       <x:c r="B44" s="10"/>
       <x:c r="D44" s="10"/>
+      <x:c r="H44" s="11"/>
     </x:row>
     <x:row r="45">
       <x:c r="B45" s="10"/>
       <x:c r="D45" s="10"/>
+      <x:c r="H45" s="11"/>
     </x:row>
     <x:row r="46">
       <x:c r="B46" s="10"/>
       <x:c r="D46" s="10"/>
+      <x:c r="H46" s="11"/>
     </x:row>
     <x:row r="47">
       <x:c r="B47" s="10"/>
       <x:c r="D47" s="10"/>
+      <x:c r="H47" s="11"/>
     </x:row>
     <x:row r="48">
       <x:c r="B48" s="10"/>
       <x:c r="D48" s="10"/>
+      <x:c r="H48" s="11"/>
     </x:row>
     <x:row r="49">
       <x:c r="B49" s="10"/>
       <x:c r="D49" s="10"/>
+      <x:c r="H49" s="11"/>
     </x:row>
     <x:row r="50">
       <x:c r="B50" s="10"/>
       <x:c r="D50" s="10"/>
+      <x:c r="H50" s="11"/>
     </x:row>
     <x:row r="51">
       <x:c r="B51" s="10"/>
       <x:c r="D51" s="10"/>
+      <x:c r="H51" s="11"/>
     </x:row>
     <x:row r="52">
       <x:c r="B52" s="10"/>
       <x:c r="D52" s="10"/>
+      <x:c r="H52" s="11"/>
     </x:row>
     <x:row r="53">
       <x:c r="B53" s="10"/>
       <x:c r="D53" s="10"/>
+      <x:c r="H53" s="11"/>
     </x:row>
     <x:row r="54">
       <x:c r="B54" s="10"/>
       <x:c r="D54" s="10"/>
+      <x:c r="H54" s="11"/>
     </x:row>
     <x:row r="55">
       <x:c r="B55" s="10"/>
       <x:c r="D55" s="10"/>
+      <x:c r="H55" s="11"/>
     </x:row>
     <x:row r="56">
       <x:c r="B56" s="10"/>
       <x:c r="D56" s="10"/>
+      <x:c r="H56" s="11"/>
     </x:row>
     <x:row r="57">
       <x:c r="B57" s="10"/>
       <x:c r="D57" s="10"/>
+      <x:c r="H57" s="11"/>
     </x:row>
     <x:row r="58">
       <x:c r="B58" s="10"/>
       <x:c r="D58" s="10"/>
+      <x:c r="H58" s="11"/>
     </x:row>
     <x:row r="59">
       <x:c r="B59" s="10"/>
       <x:c r="D59" s="10"/>
+      <x:c r="H59" s="11"/>
     </x:row>
     <x:row r="60">
       <x:c r="B60" s="10"/>
       <x:c r="D60" s="10"/>
+      <x:c r="H60" s="11"/>
     </x:row>
     <x:row r="61">
       <x:c r="B61" s="10"/>
       <x:c r="D61" s="10"/>
+      <x:c r="H61" s="11"/>
     </x:row>
     <x:row r="62">
       <x:c r="B62" s="10"/>
       <x:c r="D62" s="10"/>
+      <x:c r="H62" s="11"/>
     </x:row>
     <x:row r="63">
       <x:c r="B63" s="10"/>
       <x:c r="D63" s="10"/>
+      <x:c r="H63" s="11"/>
     </x:row>
     <x:row r="64">
       <x:c r="B64" s="10"/>
       <x:c r="D64" s="10"/>
+      <x:c r="H64" s="11"/>
     </x:row>
     <x:row r="65">
       <x:c r="B65" s="10"/>
       <x:c r="D65" s="10"/>
+      <x:c r="H65" s="11"/>
     </x:row>
     <x:row r="66">
       <x:c r="B66" s="10"/>
       <x:c r="D66" s="10"/>
+      <x:c r="H66" s="11"/>
     </x:row>
     <x:row r="67">
       <x:c r="B67" s="10"/>
       <x:c r="D67" s="10"/>
+      <x:c r="H67" s="11"/>
     </x:row>
     <x:row r="68">
       <x:c r="B68" s="10"/>
       <x:c r="D68" s="10"/>
+      <x:c r="H68" s="11"/>
     </x:row>
     <x:row r="69">
       <x:c r="B69" s="10"/>
       <x:c r="D69" s="10"/>
+      <x:c r="H69" s="11"/>
     </x:row>
     <x:row r="70">
       <x:c r="B70" s="10"/>
       <x:c r="D70" s="10"/>
+      <x:c r="H70" s="11"/>
     </x:row>
     <x:row r="71">
       <x:c r="B71" s="10"/>
       <x:c r="D71" s="10"/>
+      <x:c r="H71" s="11"/>
     </x:row>
     <x:row r="72">
       <x:c r="B72" s="10"/>
       <x:c r="D72" s="10"/>
+      <x:c r="H72" s="11"/>
     </x:row>
     <x:row r="73">
       <x:c r="B73" s="10"/>
       <x:c r="D73" s="10"/>
+      <x:c r="H73" s="11"/>
     </x:row>
     <x:row r="74">
       <x:c r="B74" s="10"/>
       <x:c r="D74" s="10"/>
+      <x:c r="H74" s="11"/>
     </x:row>
     <x:row r="75">
       <x:c r="B75" s="10"/>
       <x:c r="D75" s="10"/>
+      <x:c r="H75" s="11"/>
     </x:row>
     <x:row r="76">
       <x:c r="B76" s="10"/>
       <x:c r="D76" s="10"/>
+      <x:c r="H76" s="11"/>
     </x:row>
     <x:row r="77">
       <x:c r="B77" s="10"/>
       <x:c r="D77" s="10"/>
+      <x:c r="H77" s="11"/>
     </x:row>
     <x:row r="78">
       <x:c r="B78" s="10"/>
       <x:c r="D78" s="10"/>
+      <x:c r="H78" s="11"/>
     </x:row>
     <x:row r="79">
       <x:c r="B79" s="10"/>
       <x:c r="D79" s="10"/>
+      <x:c r="H79" s="11"/>
     </x:row>
     <x:row r="80">
       <x:c r="B80" s="10"/>
       <x:c r="D80" s="10"/>
+      <x:c r="H80" s="11"/>
     </x:row>
     <x:row r="81">
       <x:c r="B81" s="10"/>
       <x:c r="D81" s="10"/>
+      <x:c r="H81" s="11"/>
     </x:row>
     <x:row r="82">
       <x:c r="B82" s="10"/>
       <x:c r="D82" s="10"/>
+      <x:c r="H82" s="11"/>
     </x:row>
     <x:row r="83">
       <x:c r="B83" s="10"/>
       <x:c r="D83" s="10"/>
+      <x:c r="H83" s="11"/>
     </x:row>
     <x:row r="84">
       <x:c r="B84" s="10"/>
       <x:c r="D84" s="10"/>
+      <x:c r="H84" s="11"/>
     </x:row>
     <x:row r="85">
       <x:c r="B85" s="10"/>
       <x:c r="D85" s="10"/>
+      <x:c r="H85" s="11"/>
     </x:row>
     <x:row r="86">
       <x:c r="B86" s="10"/>
       <x:c r="D86" s="10"/>
+      <x:c r="H86" s="11"/>
     </x:row>
     <x:row r="87">
       <x:c r="B87" s="10"/>
       <x:c r="D87" s="10"/>
+      <x:c r="H87" s="11"/>
     </x:row>
     <x:row r="88">
       <x:c r="B88" s="10"/>
       <x:c r="D88" s="10"/>
+      <x:c r="H88" s="11"/>
     </x:row>
     <x:row r="89">
       <x:c r="B89" s="10"/>
       <x:c r="D89" s="10"/>
+      <x:c r="H89" s="11"/>
     </x:row>
     <x:row r="90">
       <x:c r="B90" s="10"/>
       <x:c r="D90" s="10"/>
+      <x:c r="H90" s="11"/>
     </x:row>
     <x:row r="91">
       <x:c r="B91" s="10"/>
       <x:c r="D91" s="10"/>
+      <x:c r="H91" s="11"/>
     </x:row>
     <x:row r="92">
       <x:c r="B92" s="10"/>
       <x:c r="D92" s="10"/>
+      <x:c r="H92" s="11"/>
     </x:row>
     <x:row r="93">
       <x:c r="B93" s="10"/>
       <x:c r="D93" s="10"/>
+      <x:c r="H93" s="11"/>
     </x:row>
     <x:row r="94">
       <x:c r="B94" s="10"/>
       <x:c r="D94" s="10"/>
+      <x:c r="H94" s="11"/>
     </x:row>
     <x:row r="95">
       <x:c r="B95" s="10"/>
       <x:c r="D95" s="10"/>
+      <x:c r="H95" s="11"/>
     </x:row>
     <x:row r="96">
       <x:c r="B96" s="10"/>
       <x:c r="D96" s="10"/>
+      <x:c r="H96" s="11"/>
     </x:row>
     <x:row r="97">
       <x:c r="B97" s="10"/>
       <x:c r="D97" s="10"/>
+      <x:c r="H97" s="11"/>
     </x:row>
     <x:row r="98">
       <x:c r="B98" s="10"/>
       <x:c r="D98" s="10"/>
+      <x:c r="H98" s="11"/>
     </x:row>
     <x:row r="99">
       <x:c r="B99" s="10"/>
       <x:c r="D99" s="10"/>
+      <x:c r="H99" s="11"/>
     </x:row>
     <x:row r="100">
       <x:c r="B100" s="10"/>
       <x:c r="D100" s="10"/>
+      <x:c r="H100" s="11"/>
     </x:row>
     <x:row r="101">
       <x:c r="B101" s="10"/>
       <x:c r="D101" s="10"/>
+      <x:c r="H101" s="11"/>
     </x:row>
     <x:row r="102">
       <x:c r="B102" s="10"/>
       <x:c r="D102" s="10"/>
+      <x:c r="H102" s="11"/>
     </x:row>
     <x:row r="103">
       <x:c r="B103" s="10"/>
       <x:c r="D103" s="10"/>
+      <x:c r="H103" s="11"/>
     </x:row>
     <x:row r="104">
       <x:c r="B104" s="10"/>
       <x:c r="D104" s="10"/>
+      <x:c r="H104" s="11"/>
     </x:row>
     <x:row r="105">
       <x:c r="B105" s="10"/>
       <x:c r="D105" s="10"/>
+      <x:c r="H105" s="11"/>
     </x:row>
     <x:row r="106">
       <x:c r="B106" s="10"/>
       <x:c r="D106" s="10"/>
+      <x:c r="H106" s="11"/>
     </x:row>
     <x:row r="107">
       <x:c r="B107" s="10"/>
       <x:c r="D107" s="10"/>
+      <x:c r="H107" s="11"/>
     </x:row>
     <x:row r="108">
       <x:c r="B108" s="10"/>
       <x:c r="D108" s="10"/>
+      <x:c r="H108" s="11"/>
     </x:row>
     <x:row r="109">
       <x:c r="B109" s="10"/>
       <x:c r="D109" s="10"/>
+      <x:c r="H109" s="11"/>
     </x:row>
     <x:row r="110">
       <x:c r="B110" s="10"/>
       <x:c r="D110" s="10"/>
+      <x:c r="H110" s="11"/>
     </x:row>
     <x:row r="111">
       <x:c r="B111" s="10"/>
       <x:c r="D111" s="10"/>
+      <x:c r="H111" s="11"/>
     </x:row>
     <x:row r="112">
       <x:c r="B112" s="10"/>
       <x:c r="D112" s="10"/>
+      <x:c r="H112" s="11"/>
     </x:row>
     <x:row r="113">
       <x:c r="B113" s="10"/>
       <x:c r="D113" s="10"/>
+      <x:c r="H113" s="11"/>
     </x:row>
     <x:row r="114">
       <x:c r="B114" s="10"/>
       <x:c r="D114" s="10"/>
+      <x:c r="H114" s="11"/>
     </x:row>
     <x:row r="115">
       <x:c r="B115" s="10"/>
       <x:c r="D115" s="10"/>
+      <x:c r="H115" s="11"/>
     </x:row>
     <x:row r="116">
       <x:c r="B116" s="10"/>
       <x:c r="D116" s="10"/>
+      <x:c r="H116" s="11"/>
     </x:row>
     <x:row r="117">
       <x:c r="B117" s="10"/>
       <x:c r="D117" s="10"/>
+      <x:c r="H117" s="11"/>
     </x:row>
     <x:row r="118">
       <x:c r="B118" s="10"/>
       <x:c r="D118" s="10"/>
+      <x:c r="H118" s="11"/>
     </x:row>
     <x:row r="119">
       <x:c r="B119" s="10"/>
       <x:c r="D119" s="10"/>
+      <x:c r="H119" s="11"/>
     </x:row>
     <x:row r="120">
       <x:c r="B120" s="10"/>
       <x:c r="D120" s="10"/>
+      <x:c r="H120" s="11"/>
     </x:row>
     <x:row r="121">
       <x:c r="B121" s="10"/>
       <x:c r="D121" s="10"/>
+      <x:c r="H121" s="11"/>
     </x:row>
     <x:row r="122">
       <x:c r="B122" s="10"/>
       <x:c r="D122" s="10"/>
+      <x:c r="H122" s="11"/>
     </x:row>
     <x:row r="123">
       <x:c r="B123" s="10"/>
       <x:c r="D123" s="10"/>
+      <x:c r="H123" s="11"/>
     </x:row>
     <x:row r="124">
       <x:c r="B124" s="10"/>
       <x:c r="D124" s="10"/>
+      <x:c r="H124" s="11"/>
     </x:row>
     <x:row r="125">
       <x:c r="B125" s="10"/>
       <x:c r="D125" s="10"/>
+      <x:c r="H125" s="11"/>
     </x:row>
     <x:row r="126">
       <x:c r="B126" s="10"/>
       <x:c r="D126" s="10"/>
+      <x:c r="H126" s="11"/>
     </x:row>
     <x:row r="127">
       <x:c r="B127" s="10"/>
       <x:c r="D127" s="10"/>
+      <x:c r="H127" s="11"/>
     </x:row>
     <x:row r="128">
       <x:c r="B128" s="10"/>
       <x:c r="D128" s="10"/>
+      <x:c r="H128" s="11"/>
     </x:row>
     <x:row r="129">
       <x:c r="B129" s="10"/>
       <x:c r="D129" s="10"/>
+      <x:c r="H129" s="11"/>
     </x:row>
     <x:row r="130">
       <x:c r="B130" s="10"/>
       <x:c r="D130" s="10"/>
+      <x:c r="H130" s="11"/>
     </x:row>
     <x:row r="131">
       <x:c r="B131" s="10"/>
       <x:c r="D131" s="10"/>
+      <x:c r="H131" s="11"/>
     </x:row>
     <x:row r="132">
       <x:c r="B132" s="10"/>
       <x:c r="D132" s="10"/>
+      <x:c r="H132" s="11"/>
     </x:row>
     <x:row r="133">
       <x:c r="B133" s="10"/>
       <x:c r="D133" s="10"/>
+      <x:c r="H133" s="11"/>
     </x:row>
     <x:row r="134">
       <x:c r="B134" s="10"/>
       <x:c r="D134" s="10"/>
+      <x:c r="H134" s="11"/>
     </x:row>
     <x:row r="135">
       <x:c r="B135" s="10"/>
       <x:c r="D135" s="10"/>
+      <x:c r="H135" s="11"/>
     </x:row>
     <x:row r="136">
       <x:c r="B136" s="10"/>
       <x:c r="D136" s="10"/>
+      <x:c r="H136" s="11"/>
     </x:row>
     <x:row r="137">
       <x:c r="B137" s="10"/>
       <x:c r="D137" s="10"/>
+      <x:c r="H137" s="11"/>
     </x:row>
     <x:row r="138">
       <x:c r="B138" s="10"/>
       <x:c r="D138" s="10"/>
+      <x:c r="H138" s="11"/>
     </x:row>
     <x:row r="139">
       <x:c r="B139" s="10"/>
       <x:c r="D139" s="10"/>
+      <x:c r="H139" s="11"/>
     </x:row>
     <x:row r="140">
       <x:c r="B140" s="10"/>
       <x:c r="D140" s="10"/>
+      <x:c r="H140" s="11"/>
     </x:row>
     <x:row r="141">
       <x:c r="B141" s="10"/>
       <x:c r="D141" s="10"/>
+      <x:c r="H141" s="11"/>
     </x:row>
     <x:row r="142">
       <x:c r="B142" s="10"/>
       <x:c r="D142" s="10"/>
+      <x:c r="H142" s="11"/>
     </x:row>
     <x:row r="143">
       <x:c r="B143" s="10"/>
       <x:c r="D143" s="10"/>
+      <x:c r="H143" s="11"/>
     </x:row>
     <x:row r="144">
       <x:c r="B144" s="10"/>
       <x:c r="D144" s="10"/>
+      <x:c r="H144" s="11"/>
     </x:row>
     <x:row r="145">
       <x:c r="B145" s="10"/>
       <x:c r="D145" s="10"/>
+      <x:c r="H145" s="11"/>
     </x:row>
     <x:row r="146">
       <x:c r="B146" s="10"/>
       <x:c r="D146" s="10"/>
+      <x:c r="H146" s="11"/>
     </x:row>
     <x:row r="147">
       <x:c r="B147" s="10"/>
       <x:c r="D147" s="10"/>
+      <x:c r="H147" s="11"/>
     </x:row>
     <x:row r="148">
       <x:c r="B148" s="10"/>
       <x:c r="D148" s="10"/>
+      <x:c r="H148" s="11"/>
     </x:row>
     <x:row r="149">
       <x:c r="B149" s="10"/>
       <x:c r="D149" s="10"/>
+      <x:c r="H149" s="11"/>
     </x:row>
     <x:row r="150">
       <x:c r="B150" s="10"/>
       <x:c r="D150" s="10"/>
+      <x:c r="H150" s="11"/>
     </x:row>
     <x:row r="151">
       <x:c r="B151" s="10"/>
       <x:c r="D151" s="10"/>
+      <x:c r="H151" s="11"/>
     </x:row>
     <x:row r="152">
       <x:c r="B152" s="10"/>
       <x:c r="D152" s="10"/>
+      <x:c r="H152" s="11"/>
     </x:row>
     <x:row r="153">
       <x:c r="B153" s="10"/>
       <x:c r="D153" s="10"/>
+      <x:c r="H153" s="11"/>
     </x:row>
     <x:row r="154">
       <x:c r="B154" s="10"/>
       <x:c r="D154" s="10"/>
+      <x:c r="H154" s="11"/>
     </x:row>
     <x:row r="155">
       <x:c r="B155" s="10"/>
       <x:c r="D155" s="10"/>
+      <x:c r="H155" s="11"/>
     </x:row>
     <x:row r="156">
       <x:c r="B156" s="10"/>
       <x:c r="D156" s="10"/>
+      <x:c r="H156" s="11"/>
     </x:row>
     <x:row r="157">
       <x:c r="B157" s="10"/>
       <x:c r="D157" s="10"/>
+      <x:c r="H157" s="11"/>
     </x:row>
     <x:row r="158">
       <x:c r="B158" s="10"/>
       <x:c r="D158" s="10"/>
+      <x:c r="H158" s="11"/>
     </x:row>
     <x:row r="159">
       <x:c r="B159" s="10"/>
       <x:c r="D159" s="10"/>
+      <x:c r="H159" s="11"/>
     </x:row>
     <x:row r="160">
       <x:c r="B160" s="10"/>
       <x:c r="D160" s="10"/>
+      <x:c r="H160" s="11"/>
     </x:row>
     <x:row r="161">
       <x:c r="B161" s="10"/>
       <x:c r="D161" s="10"/>
+      <x:c r="H161" s="11"/>
     </x:row>
     <x:row r="162">
       <x:c r="B162" s="10"/>
       <x:c r="D162" s="10"/>
+      <x:c r="H162" s="11"/>
     </x:row>
     <x:row r="163">
       <x:c r="B163" s="10"/>
       <x:c r="D163" s="10"/>
+      <x:c r="H163" s="11"/>
     </x:row>
     <x:row r="164">
       <x:c r="B164" s="10"/>
       <x:c r="D164" s="10"/>
+      <x:c r="H164" s="11"/>
     </x:row>
     <x:row r="165">
       <x:c r="B165" s="10"/>
       <x:c r="D165" s="10"/>
+      <x:c r="H165" s="11"/>
     </x:row>
     <x:row r="166">
       <x:c r="B166" s="10"/>
       <x:c r="D166" s="10"/>
+      <x:c r="H166" s="11"/>
     </x:row>
     <x:row r="167">
       <x:c r="B167" s="10"/>
       <x:c r="D167" s="10"/>
+      <x:c r="H167" s="11"/>
     </x:row>
     <x:row r="168">
       <x:c r="B168" s="10"/>
       <x:c r="D168" s="10"/>
+      <x:c r="H168" s="11"/>
     </x:row>
     <x:row r="169">
       <x:c r="B169" s="10"/>
       <x:c r="D169" s="10"/>
+      <x:c r="H169" s="11"/>
     </x:row>
     <x:row r="170">
       <x:c r="B170" s="10"/>
       <x:c r="D170" s="10"/>
+      <x:c r="H170" s="11"/>
     </x:row>
     <x:row r="171">
       <x:c r="B171" s="10"/>
       <x:c r="D171" s="10"/>
+      <x:c r="H171" s="11"/>
     </x:row>
     <x:row r="172">
       <x:c r="B172" s="10"/>
       <x:c r="D172" s="10"/>
+      <x:c r="H172" s="11"/>
     </x:row>
     <x:row r="173">
       <x:c r="B173" s="10"/>
       <x:c r="D173" s="10"/>
+      <x:c r="H173" s="11"/>
     </x:row>
     <x:row r="174">
       <x:c r="B174" s="10"/>
       <x:c r="D174" s="10"/>
+      <x:c r="H174" s="11"/>
     </x:row>
     <x:row r="175">
       <x:c r="B175" s="10"/>
       <x:c r="D175" s="10"/>
+      <x:c r="H175" s="11"/>
     </x:row>
     <x:row r="176">
       <x:c r="B176" s="10"/>
       <x:c r="D176" s="10"/>
+      <x:c r="H176" s="11"/>
     </x:row>
     <x:row r="177">
       <x:c r="B177" s="10"/>
       <x:c r="D177" s="10"/>
+      <x:c r="H177" s="11"/>
     </x:row>
     <x:row r="178">
       <x:c r="B178" s="10"/>
       <x:c r="D178" s="10"/>
+      <x:c r="H178" s="11"/>
     </x:row>
     <x:row r="179">
       <x:c r="B179" s="10"/>
       <x:c r="D179" s="10"/>
+      <x:c r="H179" s="11"/>
     </x:row>
     <x:row r="180">
       <x:c r="B180" s="10"/>
       <x:c r="D180" s="10"/>
+      <x:c r="H180" s="11"/>
     </x:row>
     <x:row r="181">
       <x:c r="B181" s="10"/>
       <x:c r="D181" s="10"/>
+      <x:c r="H181" s="11"/>
     </x:row>
     <x:row r="182">
       <x:c r="B182" s="10"/>
       <x:c r="D182" s="10"/>
+      <x:c r="H182" s="11"/>
     </x:row>
     <x:row r="183">
       <x:c r="B183" s="10"/>
       <x:c r="D183" s="10"/>
+      <x:c r="H183" s="11"/>
     </x:row>
     <x:row r="184">
       <x:c r="B184" s="10"/>
       <x:c r="D184" s="10"/>
+      <x:c r="H184" s="11"/>
     </x:row>
     <x:row r="185">
       <x:c r="B185" s="10"/>
       <x:c r="D185" s="10"/>
+      <x:c r="H185" s="11"/>
     </x:row>
     <x:row r="186">
       <x:c r="B186" s="10"/>
       <x:c r="D186" s="10"/>
+      <x:c r="H186" s="11"/>
     </x:row>
     <x:row r="187">
       <x:c r="B187" s="10"/>
       <x:c r="D187" s="10"/>
+      <x:c r="H187" s="11"/>
     </x:row>
     <x:row r="188">
       <x:c r="B188" s="10"/>
       <x:c r="D188" s="10"/>
+      <x:c r="H188" s="11"/>
     </x:row>
     <x:row r="189">
       <x:c r="B189" s="10"/>
       <x:c r="D189" s="10"/>
+      <x:c r="H189" s="11"/>
     </x:row>
     <x:row r="190">
       <x:c r="B190" s="10"/>
       <x:c r="D190" s="10"/>
+      <x:c r="H190" s="11"/>
     </x:row>
     <x:row r="191">
       <x:c r="B191" s="10"/>
       <x:c r="D191" s="10"/>
+      <x:c r="H191" s="11"/>
     </x:row>
     <x:row r="192">
       <x:c r="B192" s="10"/>
       <x:c r="D192" s="10"/>
+      <x:c r="H192" s="11"/>
     </x:row>
     <x:row r="193">
       <x:c r="B193" s="10"/>
       <x:c r="D193" s="10"/>
+      <x:c r="H193" s="11"/>
     </x:row>
     <x:row r="194">
       <x:c r="B194" s="10"/>
       <x:c r="D194" s="10"/>
+      <x:c r="H194" s="11"/>
     </x:row>
     <x:row r="195">
       <x:c r="B195" s="10"/>
       <x:c r="D195" s="10"/>
+      <x:c r="H195" s="11"/>
     </x:row>
     <x:row r="196">
       <x:c r="B196" s="10"/>
       <x:c r="D196" s="10"/>
+      <x:c r="H196" s="11"/>
     </x:row>
     <x:row r="197">
       <x:c r="B197" s="10"/>
       <x:c r="D197" s="10"/>
+      <x:c r="H197" s="11"/>
     </x:row>
     <x:row r="198">
       <x:c r="B198" s="10"/>
       <x:c r="D198" s="10"/>
+      <x:c r="H198" s="11"/>
     </x:row>
     <x:row r="199">
       <x:c r="B199" s="10"/>
       <x:c r="D199" s="10"/>
+      <x:c r="H199" s="11"/>
     </x:row>
     <x:row r="200">
       <x:c r="B200" s="10"/>
       <x:c r="D200" s="10"/>
+      <x:c r="H200" s="11"/>
     </x:row>
     <x:row r="201">
       <x:c r="B201" s="10"/>
       <x:c r="D201" s="10"/>
+      <x:c r="H201" s="11"/>
     </x:row>
     <x:row r="202">
       <x:c r="B202" s="10"/>
       <x:c r="D202" s="10"/>
+      <x:c r="H202" s="11"/>
     </x:row>
     <x:row r="203">
       <x:c r="B203" s="10"/>
       <x:c r="D203" s="10"/>
+      <x:c r="H203" s="11"/>
     </x:row>
     <x:row r="204">
       <x:c r="B204" s="10"/>
       <x:c r="D204" s="10"/>
+      <x:c r="H204" s="11"/>
     </x:row>
     <x:row r="205">
       <x:c r="B205" s="10"/>
       <x:c r="D205" s="10"/>
+      <x:c r="H205" s="11"/>
     </x:row>
     <x:row r="206">
       <x:c r="B206" s="10"/>
       <x:c r="D206" s="10"/>
+      <x:c r="H206" s="11"/>
     </x:row>
     <x:row r="207">
       <x:c r="B207" s="10"/>
       <x:c r="D207" s="10"/>
+      <x:c r="H207" s="11"/>
     </x:row>
     <x:row r="208">
       <x:c r="B208" s="10"/>
       <x:c r="D208" s="10"/>
+      <x:c r="H208" s="11"/>
     </x:row>
     <x:row r="209">
       <x:c r="B209" s="10"/>
       <x:c r="D209" s="10"/>
+      <x:c r="H209" s="11"/>
     </x:row>
     <x:row r="210">
       <x:c r="B210" s="10"/>
       <x:c r="D210" s="10"/>
+      <x:c r="H210" s="11"/>
     </x:row>
     <x:row r="211">
       <x:c r="B211" s="10"/>
       <x:c r="D211" s="10"/>
+      <x:c r="H211" s="11"/>
     </x:row>
     <x:row r="212">
       <x:c r="B212" s="10"/>
       <x:c r="D212" s="10"/>
+      <x:c r="H212" s="11"/>
     </x:row>
     <x:row r="213">
       <x:c r="B213" s="10"/>
       <x:c r="D213" s="10"/>
+      <x:c r="H213" s="11"/>
     </x:row>
     <x:row r="214">
       <x:c r="B214" s="10"/>
       <x:c r="D214" s="10"/>
+      <x:c r="H214" s="11"/>
     </x:row>
     <x:row r="215">
       <x:c r="B215" s="10"/>
       <x:c r="D215" s="10"/>
+      <x:c r="H215" s="11"/>
     </x:row>
     <x:row r="216">
       <x:c r="B216" s="10"/>
       <x:c r="D216" s="10"/>
+      <x:c r="H216" s="11"/>
     </x:row>
     <x:row r="217">
       <x:c r="B217" s="10"/>
       <x:c r="D217" s="10"/>
+      <x:c r="H217" s="11"/>
     </x:row>
     <x:row r="218">
       <x:c r="B218" s="10"/>
       <x:c r="D218" s="10"/>
+      <x:c r="H218" s="11"/>
     </x:row>
     <x:row r="219">
       <x:c r="B219" s="10"/>
       <x:c r="D219" s="10"/>
+      <x:c r="H219" s="11"/>
     </x:row>
     <x:row r="220">
       <x:c r="B220" s="10"/>
       <x:c r="D220" s="10"/>
+      <x:c r="H220" s="11"/>
     </x:row>
     <x:row r="221">
       <x:c r="B221" s="10"/>
       <x:c r="D221" s="10"/>
+      <x:c r="H221" s="11"/>
     </x:row>
     <x:row r="222">
       <x:c r="B222" s="10"/>
       <x:c r="D222" s="10"/>
+      <x:c r="H222" s="11"/>
     </x:row>
     <x:row r="223">
       <x:c r="B223" s="10"/>
       <x:c r="D223" s="10"/>
+      <x:c r="H223" s="11"/>
     </x:row>
     <x:row r="224">
       <x:c r="B224" s="10"/>
       <x:c r="D224" s="10"/>
+      <x:c r="H224" s="11"/>
     </x:row>
     <x:row r="225">
       <x:c r="B225" s="10"/>
       <x:c r="D225" s="10"/>
+      <x:c r="H225" s="11"/>
     </x:row>
     <x:row r="226">
       <x:c r="B226" s="10"/>
       <x:c r="D226" s="10"/>
+      <x:c r="H226" s="11"/>
     </x:row>
     <x:row r="227">
       <x:c r="B227" s="10"/>
       <x:c r="D227" s="10"/>
+      <x:c r="H227" s="11"/>
     </x:row>
     <x:row r="228">
       <x:c r="B228" s="10"/>
       <x:c r="D228" s="10"/>
+      <x:c r="H228" s="11"/>
     </x:row>
     <x:row r="229">
       <x:c r="B229" s="10"/>
       <x:c r="D229" s="10"/>
+      <x:c r="H229" s="11"/>
     </x:row>
     <x:row r="230">
       <x:c r="B230" s="10"/>
       <x:c r="D230" s="10"/>
+      <x:c r="H230" s="11"/>
     </x:row>
     <x:row r="231">
       <x:c r="B231" s="10"/>
       <x:c r="D231" s="10"/>
+      <x:c r="H231" s="11"/>
     </x:row>
     <x:row r="232">
       <x:c r="B232" s="10"/>
       <x:c r="D232" s="10"/>
+      <x:c r="H232" s="11"/>
     </x:row>
     <x:row r="233">
       <x:c r="B233" s="10"/>
       <x:c r="D233" s="10"/>
+      <x:c r="H233" s="11"/>
     </x:row>
     <x:row r="234">
       <x:c r="B234" s="10"/>
       <x:c r="D234" s="10"/>
+      <x:c r="H234" s="11"/>
     </x:row>
     <x:row r="235">
       <x:c r="B235" s="10"/>
       <x:c r="D235" s="10"/>
+      <x:c r="H235" s="11"/>
     </x:row>
     <x:row r="236">
       <x:c r="B236" s="10"/>
       <x:c r="D236" s="10"/>
+      <x:c r="H236" s="11"/>
     </x:row>
     <x:row r="237">
       <x:c r="B237" s="10"/>
       <x:c r="D237" s="10"/>
+      <x:c r="H237" s="11"/>
     </x:row>
     <x:row r="238">
       <x:c r="B238" s="10"/>
       <x:c r="D238" s="10"/>
+      <x:c r="H238" s="11"/>
     </x:row>
     <x:row r="239">
       <x:c r="B239" s="10"/>
       <x:c r="D239" s="10"/>
+      <x:c r="H239" s="11"/>
     </x:row>
     <x:row r="240">
       <x:c r="B240" s="10"/>
       <x:c r="D240" s="10"/>
+      <x:c r="H240" s="11"/>
     </x:row>
     <x:row r="241">
       <x:c r="B241" s="10"/>
       <x:c r="D241" s="10"/>
+      <x:c r="H241" s="11"/>
     </x:row>
     <x:row r="242">
       <x:c r="B242" s="10"/>
       <x:c r="D242" s="10"/>
+      <x:c r="H242" s="11"/>
     </x:row>
     <x:row r="243">
       <x:c r="B243" s="10"/>
       <x:c r="D243" s="10"/>
+      <x:c r="H243" s="11"/>
     </x:row>
     <x:row r="244">
       <x:c r="B244" s="10"/>
       <x:c r="D244" s="10"/>
+      <x:c r="H244" s="11"/>
     </x:row>
     <x:row r="245">
       <x:c r="B245" s="10"/>
       <x:c r="D245" s="10"/>
+      <x:c r="H245" s="11"/>
     </x:row>
     <x:row r="246">
       <x:c r="B246" s="10"/>
       <x:c r="D246" s="10"/>
+      <x:c r="H246" s="11"/>
     </x:row>
     <x:row r="247">
       <x:c r="B247" s="10"/>
       <x:c r="D247" s="10"/>
+      <x:c r="H247" s="11"/>
     </x:row>
     <x:row r="248">
       <x:c r="B248" s="10"/>
       <x:c r="D248" s="10"/>
+      <x:c r="H248" s="11"/>
     </x:row>
     <x:row r="249">
       <x:c r="B249" s="10"/>
       <x:c r="D249" s="10"/>
+      <x:c r="H249" s="11"/>
     </x:row>
     <x:row r="250">
       <x:c r="B250" s="10"/>
       <x:c r="D250" s="10"/>
+      <x:c r="H250" s="11"/>
     </x:row>
     <x:row r="251">
       <x:c r="B251" s="10"/>
       <x:c r="D251" s="10"/>
+      <x:c r="H251" s="11"/>
     </x:row>
     <x:row r="252">
       <x:c r="B252" s="10"/>
       <x:c r="D252" s="10"/>
+      <x:c r="H252" s="11"/>
     </x:row>
     <x:row r="253">
       <x:c r="B253" s="10"/>
       <x:c r="D253" s="10"/>
+      <x:c r="H253" s="11"/>
     </x:row>
     <x:row r="254">
       <x:c r="B254" s="10"/>
       <x:c r="D254" s="10"/>
+      <x:c r="H254" s="11"/>
     </x:row>
     <x:row r="255">
       <x:c r="B255" s="10"/>
       <x:c r="D255" s="10"/>
+      <x:c r="H255" s="11"/>
     </x:row>
     <x:row r="256">
       <x:c r="B256" s="10"/>
       <x:c r="D256" s="10"/>
+      <x:c r="H256" s="11"/>
     </x:row>
     <x:row r="257">
       <x:c r="B257" s="10"/>
       <x:c r="D257" s="10"/>
+      <x:c r="H257" s="11"/>
     </x:row>
     <x:row r="258">
       <x:c r="B258" s="10"/>
       <x:c r="D258" s="10"/>
+      <x:c r="H258" s="11"/>
     </x:row>
     <x:row r="259">
       <x:c r="B259" s="10"/>
       <x:c r="D259" s="10"/>
+      <x:c r="H259" s="11"/>
     </x:row>
     <x:row r="260">
       <x:c r="B260" s="10"/>
       <x:c r="D260" s="10"/>
+      <x:c r="H260" s="11"/>
     </x:row>
     <x:row r="261">
       <x:c r="B261" s="10"/>
       <x:c r="D261" s="10"/>
+      <x:c r="H261" s="11"/>
     </x:row>
     <x:row r="262">
       <x:c r="B262" s="10"/>
       <x:c r="D262" s="10"/>
+      <x:c r="H262" s="11"/>
     </x:row>
     <x:row r="263">
       <x:c r="B263" s="10"/>
       <x:c r="D263" s="10"/>
+      <x:c r="H263" s="11"/>
     </x:row>
     <x:row r="264">
       <x:c r="B264" s="10"/>
       <x:c r="D264" s="10"/>
+      <x:c r="H264" s="11"/>
     </x:row>
     <x:row r="265">
       <x:c r="B265" s="10"/>
       <x:c r="D265" s="10"/>
+      <x:c r="H265" s="11"/>
     </x:row>
     <x:row r="266">
       <x:c r="B266" s="10"/>
       <x:c r="D266" s="10"/>
+      <x:c r="H266" s="11"/>
     </x:row>
     <x:row r="267">
       <x:c r="B267" s="10"/>
       <x:c r="D267" s="10"/>
+      <x:c r="H267" s="11"/>
     </x:row>
     <x:row r="268">
       <x:c r="B268" s="10"/>
       <x:c r="D268" s="10"/>
+      <x:c r="H268" s="11"/>
     </x:row>
     <x:row r="269">
       <x:c r="B269" s="10"/>
       <x:c r="D269" s="10"/>
+      <x:c r="H269" s="11"/>
     </x:row>
     <x:row r="270">
       <x:c r="B270" s="10"/>
       <x:c r="D270" s="10"/>
+      <x:c r="H270" s="11"/>
     </x:row>
     <x:row r="271">
       <x:c r="B271" s="10"/>
       <x:c r="D271" s="10"/>
+      <x:c r="H271" s="11"/>
     </x:row>
     <x:row r="272">
       <x:c r="B272" s="10"/>
       <x:c r="D272" s="10"/>
+      <x:c r="H272" s="11"/>
     </x:row>
     <x:row r="273">
       <x:c r="B273" s="10"/>
       <x:c r="D273" s="10"/>
+      <x:c r="H273" s="11"/>
     </x:row>
     <x:row r="274">
       <x:c r="B274" s="10"/>
       <x:c r="D274" s="10"/>
+      <x:c r="H274" s="11"/>
     </x:row>
     <x:row r="275">
       <x:c r="B275" s="10"/>
       <x:c r="D275" s="10"/>
+      <x:c r="H275" s="11"/>
     </x:row>
     <x:row r="276">
       <x:c r="B276" s="10"/>
       <x:c r="D276" s="10"/>
+      <x:c r="H276" s="11"/>
     </x:row>
     <x:row r="277">
       <x:c r="B277" s="10"/>
       <x:c r="D277" s="10"/>
+      <x:c r="H277" s="11"/>
     </x:row>
     <x:row r="278">
       <x:c r="B278" s="10"/>
       <x:c r="D278" s="10"/>
+      <x:c r="H278" s="11"/>
     </x:row>
     <x:row r="279">
       <x:c r="B279" s="10"/>
       <x:c r="D279" s="10"/>
+      <x:c r="H279" s="11"/>
     </x:row>
     <x:row r="280">
       <x:c r="B280" s="10"/>
       <x:c r="D280" s="10"/>
+      <x:c r="H280" s="11"/>
     </x:row>
     <x:row r="281">
       <x:c r="B281" s="10"/>
       <x:c r="D281" s="10"/>
+      <x:c r="H281" s="11"/>
     </x:row>
     <x:row r="282">
       <x:c r="B282" s="10"/>
       <x:c r="D282" s="10"/>
+      <x:c r="H282" s="11"/>
     </x:row>
     <x:row r="283">
       <x:c r="B283" s="10"/>
       <x:c r="D283" s="10"/>
+      <x:c r="H283" s="11"/>
     </x:row>
     <x:row r="284">
       <x:c r="B284" s="10"/>
       <x:c r="D284" s="10"/>
+      <x:c r="H284" s="11"/>
     </x:row>
     <x:row r="285">
       <x:c r="B285" s="10"/>
       <x:c r="D285" s="10"/>
+      <x:c r="H285" s="11"/>
     </x:row>
     <x:row r="286">
       <x:c r="B286" s="10"/>
       <x:c r="D286" s="10"/>
+      <x:c r="H286" s="11"/>
     </x:row>
     <x:row r="287">
       <x:c r="B287" s="10"/>
       <x:c r="D287" s="10"/>
+      <x:c r="H287" s="11"/>
     </x:row>
     <x:row r="288">
       <x:c r="B288" s="10"/>
       <x:c r="D288" s="10"/>
+      <x:c r="H288" s="11"/>
     </x:row>
     <x:row r="289">
       <x:c r="B289" s="10"/>
       <x:c r="D289" s="10"/>
+      <x:c r="H289" s="11"/>
     </x:row>
     <x:row r="290">
       <x:c r="B290" s="10"/>
       <x:c r="D290" s="10"/>
+      <x:c r="H290" s="11"/>
     </x:row>
     <x:row r="291">
       <x:c r="B291" s="10"/>
       <x:c r="D291" s="10"/>
+      <x:c r="H291" s="11"/>
     </x:row>
     <x:row r="292">
       <x:c r="B292" s="10"/>
       <x:c r="D292" s="10"/>
+      <x:c r="H292" s="11"/>
     </x:row>
     <x:row r="293">
       <x:c r="B293" s="10"/>
       <x:c r="D293" s="10"/>
+      <x:c r="H293" s="11"/>
     </x:row>
     <x:row r="294">
       <x:c r="B294" s="10"/>
       <x:c r="D294" s="10"/>
+      <x:c r="H294" s="11"/>
     </x:row>
     <x:row r="295">
       <x:c r="B295" s="10"/>
       <x:c r="D295" s="10"/>
+      <x:c r="H295" s="11"/>
     </x:row>
     <x:row r="296">
       <x:c r="B296" s="10"/>
       <x:c r="D296" s="10"/>
+      <x:c r="H296" s="11"/>
     </x:row>
     <x:row r="297">
       <x:c r="B297" s="10"/>
       <x:c r="D297" s="10"/>
+      <x:c r="H297" s="11"/>
     </x:row>
     <x:row r="298">
       <x:c r="B298" s="10"/>
       <x:c r="D298" s="10"/>
+      <x:c r="H298" s="11"/>
     </x:row>
     <x:row r="299">
       <x:c r="B299" s="10"/>
       <x:c r="D299" s="10"/>
+      <x:c r="H299" s="11"/>
     </x:row>
     <x:row r="300">
       <x:c r="B300" s="10"/>
       <x:c r="D300" s="10"/>
+      <x:c r="H300" s="11"/>
     </x:row>
     <x:row r="301">
       <x:c r="B301" s="10"/>
       <x:c r="D301" s="10"/>
+      <x:c r="H301" s="11"/>
     </x:row>
     <x:row r="302">
       <x:c r="B302" s="10"/>
       <x:c r="D302" s="10"/>
+      <x:c r="H302" s="11"/>
     </x:row>
     <x:row r="303">
       <x:c r="B303" s="10"/>
       <x:c r="D303" s="10"/>
+      <x:c r="H303" s="11"/>
     </x:row>
     <x:row r="304">
       <x:c r="B304" s="10"/>
       <x:c r="D304" s="10"/>
+      <x:c r="H304" s="11"/>
     </x:row>
     <x:row r="305">
       <x:c r="B305" s="10"/>
       <x:c r="D305" s="10"/>
+      <x:c r="H305" s="11"/>
     </x:row>
     <x:row r="306">
       <x:c r="B306" s="10"/>
       <x:c r="D306" s="10"/>
+      <x:c r="H306" s="11"/>
     </x:row>
     <x:row r="307">
       <x:c r="B307" s="10"/>
       <x:c r="D307" s="10"/>
+      <x:c r="H307" s="11"/>
     </x:row>
     <x:row r="308">
       <x:c r="B308" s="10"/>
       <x:c r="D308" s="10"/>
+      <x:c r="H308" s="11"/>
     </x:row>
     <x:row r="309">
       <x:c r="B309" s="10"/>
       <x:c r="D309" s="10"/>
+      <x:c r="H309" s="11"/>
     </x:row>
     <x:row r="310">
       <x:c r="B310" s="10"/>
       <x:c r="D310" s="10"/>
+      <x:c r="H310" s="11"/>
     </x:row>
     <x:row r="311">
       <x:c r="B311" s="10"/>
       <x:c r="D311" s="10"/>
+      <x:c r="H311" s="11"/>
     </x:row>
     <x:row r="312">
       <x:c r="B312" s="10"/>
       <x:c r="D312" s="10"/>
+      <x:c r="H312" s="11"/>
     </x:row>
     <x:row r="313">
       <x:c r="B313" s="10"/>
       <x:c r="D313" s="10"/>
+      <x:c r="H313" s="11"/>
     </x:row>
     <x:row r="314">
       <x:c r="B314" s="10"/>
       <x:c r="D314" s="10"/>
+      <x:c r="H314" s="11"/>
     </x:row>
     <x:row r="315">
       <x:c r="B315" s="10"/>
       <x:c r="D315" s="10"/>
+      <x:c r="H315" s="11"/>
     </x:row>
     <x:row r="316">
       <x:c r="B316" s="10"/>
       <x:c r="D316" s="10"/>
+      <x:c r="H316" s="11"/>
     </x:row>
     <x:row r="317">
       <x:c r="B317" s="10"/>
       <x:c r="D317" s="10"/>
+      <x:c r="H317" s="11"/>
     </x:row>
     <x:row r="318">
       <x:c r="B318" s="10"/>
       <x:c r="D318" s="10"/>
+      <x:c r="H318" s="11"/>
     </x:row>
     <x:row r="319">
       <x:c r="B319" s="10"/>
       <x:c r="D319" s="10"/>
+      <x:c r="H319" s="11"/>
     </x:row>
     <x:row r="320">
       <x:c r="B320" s="10"/>
       <x:c r="D320" s="10"/>
+      <x:c r="H320" s="11"/>
     </x:row>
     <x:row r="321">
       <x:c r="B321" s="10"/>
       <x:c r="D321" s="10"/>
+      <x:c r="H321" s="11"/>
     </x:row>
     <x:row r="322">
       <x:c r="B322" s="10"/>
       <x:c r="D322" s="10"/>
+      <x:c r="H322" s="11"/>
     </x:row>
     <x:row r="323">
       <x:c r="B323" s="10"/>
       <x:c r="D323" s="10"/>
+      <x:c r="H323" s="11"/>
     </x:row>
     <x:row r="324">
       <x:c r="B324" s="10"/>
       <x:c r="D324" s="10"/>
+      <x:c r="H324" s="11"/>
     </x:row>
     <x:row r="325">
       <x:c r="B325" s="10"/>
       <x:c r="D325" s="10"/>
+      <x:c r="H325" s="11"/>
     </x:row>
     <x:row r="326">
       <x:c r="B326" s="10"/>
       <x:c r="D326" s="10"/>
+      <x:c r="H326" s="11"/>
     </x:row>
     <x:row r="327">
       <x:c r="B327" s="10"/>
       <x:c r="D327" s="10"/>
+      <x:c r="H327" s="11"/>
     </x:row>
     <x:row r="328">
       <x:c r="B328" s="10"/>
       <x:c r="D328" s="10"/>
+      <x:c r="H328" s="11"/>
     </x:row>
     <x:row r="329">
       <x:c r="B329" s="10"/>
       <x:c r="D329" s="10"/>
+      <x:c r="H329" s="11"/>
     </x:row>
     <x:row r="330">
       <x:c r="B330" s="10"/>
       <x:c r="D330" s="10"/>
+      <x:c r="H330" s="11"/>
     </x:row>
     <x:row r="331">
       <x:c r="B331" s="10"/>
       <x:c r="D331" s="10"/>
+      <x:c r="H331" s="11"/>
     </x:row>
     <x:row r="332">
       <x:c r="B332" s="10"/>
       <x:c r="D332" s="10"/>
+      <x:c r="H332" s="11"/>
     </x:row>
     <x:row r="333">
       <x:c r="B333" s="10"/>
       <x:c r="D333" s="10"/>
+      <x:c r="H333" s="11"/>
     </x:row>
     <x:row r="334">
       <x:c r="B334" s="10"/>
       <x:c r="D334" s="10"/>
+      <x:c r="H334" s="11"/>
     </x:row>
     <x:row r="335">
       <x:c r="B335" s="10"/>
       <x:c r="D335" s="10"/>
+      <x:c r="H335" s="11"/>
     </x:row>
     <x:row r="336">
       <x:c r="B336" s="10"/>
       <x:c r="D336" s="10"/>
+      <x:c r="H336" s="11"/>
     </x:row>
     <x:row r="337">
       <x:c r="B337" s="10"/>
       <x:c r="D337" s="10"/>
+      <x:c r="H337" s="11"/>
     </x:row>
     <x:row r="338">
       <x:c r="B338" s="10"/>
       <x:c r="D338" s="10"/>
+      <x:c r="H338" s="11"/>
     </x:row>
     <x:row r="339">
       <x:c r="B339" s="10"/>
       <x:c r="D339" s="10"/>
+      <x:c r="H339" s="11"/>
     </x:row>
     <x:row r="340">
       <x:c r="B340" s="10"/>
       <x:c r="D340" s="10"/>
+      <x:c r="H340" s="11"/>
     </x:row>
     <x:row r="341">
       <x:c r="B341" s="10"/>
       <x:c r="D341" s="10"/>
+      <x:c r="H341" s="11"/>
     </x:row>
     <x:row r="342">
       <x:c r="B342" s="10"/>
       <x:c r="D342" s="10"/>
+      <x:c r="H342" s="11"/>
     </x:row>
     <x:row r="343">
       <x:c r="B343" s="10"/>
       <x:c r="D343" s="10"/>
+      <x:c r="H343" s="11"/>
     </x:row>
     <x:row r="344">
       <x:c r="B344" s="10"/>
       <x:c r="D344" s="10"/>
+      <x:c r="H344" s="11"/>
     </x:row>
     <x:row r="345">
       <x:c r="B345" s="10"/>
       <x:c r="D345" s="10"/>
+      <x:c r="H345" s="11"/>
     </x:row>
     <x:row r="346">
       <x:c r="B346" s="10"/>
       <x:c r="D346" s="10"/>
+      <x:c r="H346" s="11"/>
     </x:row>
     <x:row r="347">
       <x:c r="B347" s="10"/>
       <x:c r="D347" s="10"/>
+      <x:c r="H347" s="11"/>
     </x:row>
     <x:row r="348">
       <x:c r="B348" s="10"/>
       <x:c r="D348" s="10"/>
+      <x:c r="H348" s="11"/>
     </x:row>
     <x:row r="349">
       <x:c r="B349" s="10"/>
       <x:c r="D349" s="10"/>
+      <x:c r="H349" s="11"/>
     </x:row>
     <x:row r="350">
       <x:c r="B350" s="10"/>
       <x:c r="D350" s="10"/>
+      <x:c r="H350" s="11"/>
     </x:row>
     <x:row r="351">
       <x:c r="B351" s="10"/>
       <x:c r="D351" s="10"/>
+      <x:c r="H351" s="11"/>
     </x:row>
     <x:row r="352">
       <x:c r="B352" s="10"/>
       <x:c r="D352" s="10"/>
+      <x:c r="H352" s="11"/>
     </x:row>
     <x:row r="353">
       <x:c r="B353" s="10"/>
       <x:c r="D353" s="10"/>
+      <x:c r="H353" s="11"/>
     </x:row>
     <x:row r="354">
       <x:c r="B354" s="10"/>
       <x:c r="D354" s="10"/>
+      <x:c r="H354" s="11"/>
     </x:row>
     <x:row r="355">
       <x:c r="B355" s="10"/>
       <x:c r="D355" s="10"/>
+      <x:c r="H355" s="11"/>
     </x:row>
     <x:row r="356">
       <x:c r="B356" s="10"/>
       <x:c r="D356" s="10"/>
+      <x:c r="H356" s="11"/>
     </x:row>
     <x:row r="357">
       <x:c r="B357" s="10"/>
       <x:c r="D357" s="10"/>
+      <x:c r="H357" s="11"/>
     </x:row>
     <x:row r="358">
       <x:c r="B358" s="10"/>
       <x:c r="D358" s="10"/>
+      <x:c r="H358" s="11"/>
     </x:row>
     <x:row r="359">
       <x:c r="B359" s="10"/>
       <x:c r="D359" s="10"/>
+      <x:c r="H359" s="11"/>
     </x:row>
     <x:row r="360">
       <x:c r="B360" s="10"/>
       <x:c r="D360" s="10"/>
+      <x:c r="H360" s="11"/>
     </x:row>
     <x:row r="361">
       <x:c r="B361" s="10"/>
       <x:c r="D361" s="10"/>
+      <x:c r="H361" s="11"/>
     </x:row>
     <x:row r="362">
       <x:c r="B362" s="10"/>
       <x:c r="D362" s="10"/>
+      <x:c r="H362" s="11"/>
     </x:row>
     <x:row r="363">
       <x:c r="B363" s="10"/>
       <x:c r="D363" s="10"/>
+      <x:c r="H363" s="11"/>
     </x:row>
     <x:row r="364">
       <x:c r="B364" s="10"/>
       <x:c r="D364" s="10"/>
+      <x:c r="H364" s="11"/>
     </x:row>
     <x:row r="365">
       <x:c r="B365" s="10"/>
       <x:c r="D365" s="10"/>
+      <x:c r="H365" s="11"/>
     </x:row>
     <x:row r="366">
       <x:c r="B366" s="10"/>
       <x:c r="D366" s="10"/>
+      <x:c r="H366" s="11"/>
     </x:row>
     <x:row r="367">
       <x:c r="B367" s="10"/>
       <x:c r="D367" s="10"/>
+      <x:c r="H367" s="11"/>
     </x:row>
     <x:row r="368">
       <x:c r="B368" s="10"/>
       <x:c r="D368" s="10"/>
+      <x:c r="H368" s="11"/>
     </x:row>
     <x:row r="369">
       <x:c r="B369" s="10"/>
       <x:c r="D369" s="10"/>
+      <x:c r="H369" s="11"/>
     </x:row>
     <x:row r="370">
       <x:c r="B370" s="10"/>
       <x:c r="D370" s="10"/>
+      <x:c r="H370" s="11"/>
     </x:row>
     <x:row r="371">
       <x:c r="B371" s="10"/>
       <x:c r="D371" s="10"/>
+      <x:c r="H371" s="11"/>
     </x:row>
     <x:row r="372">
       <x:c r="B372" s="10"/>
       <x:c r="D372" s="10"/>
+      <x:c r="H372" s="11"/>
     </x:row>
     <x:row r="373">
       <x:c r="B373" s="10"/>
       <x:c r="D373" s="10"/>
+      <x:c r="H373" s="11"/>
     </x:row>
     <x:row r="374">
       <x:c r="B374" s="10"/>
       <x:c r="D374" s="10"/>
+      <x:c r="H374" s="11"/>
     </x:row>
     <x:row r="375">
       <x:c r="B375" s="10"/>
       <x:c r="D375" s="10"/>
+      <x:c r="H375" s="11"/>
     </x:row>
     <x:row r="376">
       <x:c r="B376" s="10"/>
       <x:c r="D376" s="10"/>
+      <x:c r="H376" s="11"/>
     </x:row>
     <x:row r="377">
       <x:c r="B377" s="10"/>
       <x:c r="D377" s="10"/>
+      <x:c r="H377" s="11"/>
     </x:row>
     <x:row r="378">
       <x:c r="B378" s="10"/>
       <x:c r="D378" s="10"/>
+      <x:c r="H378" s="11"/>
     </x:row>
     <x:row r="379">
       <x:c r="B379" s="10"/>
       <x:c r="D379" s="10"/>
+      <x:c r="H379" s="11"/>
     </x:row>
     <x:row r="380">
       <x:c r="B380" s="10"/>
       <x:c r="D380" s="10"/>
+      <x:c r="H380" s="11"/>
     </x:row>
     <x:row r="381">
       <x:c r="B381" s="10"/>
       <x:c r="D381" s="10"/>
+      <x:c r="H381" s="11"/>
     </x:row>
     <x:row r="382">
       <x:c r="B382" s="10"/>
       <x:c r="D382" s="10"/>
+      <x:c r="H382" s="11"/>
     </x:row>
     <x:row r="383">
       <x:c r="B383" s="10"/>
       <x:c r="D383" s="10"/>
+      <x:c r="H383" s="11"/>
     </x:row>
     <x:row r="384">
       <x:c r="B384" s="10"/>
       <x:c r="D384" s="10"/>
+      <x:c r="H384" s="11"/>
     </x:row>
     <x:row r="385">
       <x:c r="B385" s="10"/>
       <x:c r="D385" s="10"/>
+      <x:c r="H385" s="11"/>
     </x:row>
     <x:row r="386">
       <x:c r="B386" s="10"/>
       <x:c r="D386" s="10"/>
+      <x:c r="H386" s="11"/>
     </x:row>
     <x:row r="387">
       <x:c r="B387" s="10"/>
       <x:c r="D387" s="10"/>
+      <x:c r="H387" s="11"/>
     </x:row>
     <x:row r="388">
       <x:c r="B388" s="10"/>
       <x:c r="D388" s="10"/>
+      <x:c r="H388" s="11"/>
     </x:row>
     <x:row r="389">
       <x:c r="B389" s="10"/>
       <x:c r="D389" s="10"/>
+      <x:c r="H389" s="11"/>
     </x:row>
     <x:row r="390">
       <x:c r="B390" s="10"/>
       <x:c r="D390" s="10"/>
+      <x:c r="H390" s="11"/>
     </x:row>
     <x:row r="391">
       <x:c r="B391" s="10"/>
       <x:c r="D391" s="10"/>
+      <x:c r="H391" s="11"/>
     </x:row>
     <x:row r="392">
       <x:c r="B392" s="10"/>
       <x:c r="D392" s="10"/>
+      <x:c r="H392" s="11"/>
     </x:row>
     <x:row r="393">
       <x:c r="B393" s="10"/>
       <x:c r="D393" s="10"/>
+      <x:c r="H393" s="11"/>
     </x:row>
     <x:row r="394">
       <x:c r="B394" s="10"/>
       <x:c r="D394" s="10"/>
+      <x:c r="H394" s="11"/>
     </x:row>
     <x:row r="395">
       <x:c r="B395" s="10"/>
       <x:c r="D395" s="10"/>
+      <x:c r="H395" s="11"/>
     </x:row>
     <x:row r="396">
       <x:c r="B396" s="10"/>
       <x:c r="D396" s="10"/>
+      <x:c r="H396" s="11"/>
     </x:row>
     <x:row r="397">
       <x:c r="B397" s="10"/>
       <x:c r="D397" s="10"/>
+      <x:c r="H397" s="11"/>
     </x:row>
     <x:row r="398">
       <x:c r="B398" s="10"/>
       <x:c r="D398" s="10"/>
+      <x:c r="H398" s="11"/>
     </x:row>
     <x:row r="399">
       <x:c r="B399" s="10"/>
       <x:c r="D399" s="10"/>
+      <x:c r="H399" s="11"/>
     </x:row>
     <x:row r="400">
       <x:c r="B400" s="10"/>
       <x:c r="D400" s="10"/>
+      <x:c r="H400" s="11"/>
     </x:row>
     <x:row r="401">
       <x:c r="B401" s="10"/>
       <x:c r="D401" s="10"/>
+      <x:c r="H401" s="11"/>
     </x:row>
     <x:row r="402">
       <x:c r="B402" s="10"/>
       <x:c r="D402" s="10"/>
+      <x:c r="H402" s="11"/>
     </x:row>
     <x:row r="403">
       <x:c r="B403" s="10"/>
       <x:c r="D403" s="10"/>
+      <x:c r="H403" s="11"/>
     </x:row>
     <x:row r="404">
       <x:c r="B404" s="10"/>
       <x:c r="D404" s="10"/>
+      <x:c r="H404" s="11"/>
     </x:row>
     <x:row r="405">
       <x:c r="B405" s="10"/>
       <x:c r="D405" s="10"/>
+      <x:c r="H405" s="11"/>
     </x:row>
     <x:row r="406">
       <x:c r="B406" s="10"/>
       <x:c r="D406" s="10"/>
+      <x:c r="H406" s="11"/>
     </x:row>
     <x:row r="407">
       <x:c r="B407" s="10"/>
       <x:c r="D407" s="10"/>
+      <x:c r="H407" s="11"/>
     </x:row>
     <x:row r="408">
       <x:c r="B408" s="10"/>
       <x:c r="D408" s="10"/>
+      <x:c r="H408" s="11"/>
     </x:row>
     <x:row r="409">
       <x:c r="B409" s="10"/>
       <x:c r="D409" s="10"/>
+      <x:c r="H409" s="11"/>
     </x:row>
     <x:row r="410">
       <x:c r="B410" s="10"/>
       <x:c r="D410" s="10"/>
+      <x:c r="H410" s="11"/>
     </x:row>
     <x:row r="411">
       <x:c r="B411" s="10"/>
       <x:c r="D411" s="10"/>
+      <x:c r="H411" s="11"/>
     </x:row>
     <x:row r="412">
       <x:c r="B412" s="10"/>
       <x:c r="D412" s="10"/>
+      <x:c r="H412" s="11"/>
     </x:row>
     <x:row r="413">
       <x:c r="B413" s="10"/>
       <x:c r="D413" s="10"/>
+      <x:c r="H413" s="11"/>
     </x:row>
     <x:row r="414">
       <x:c r="B414" s="10"/>
       <x:c r="D414" s="10"/>
+      <x:c r="H414" s="11"/>
     </x:row>
     <x:row r="415">
       <x:c r="B415" s="10"/>
       <x:c r="D415" s="10"/>
+      <x:c r="H415" s="11"/>
     </x:row>
     <x:row r="416">
       <x:c r="B416" s="10"/>
       <x:c r="D416" s="10"/>
+      <x:c r="H416" s="11"/>
     </x:row>
     <x:row r="417">
       <x:c r="B417" s="10"/>
       <x:c r="D417" s="10"/>
+      <x:c r="H417" s="11"/>
     </x:row>
     <x:row r="418">
       <x:c r="B418" s="10"/>
       <x:c r="D418" s="10"/>
+      <x:c r="H418" s="11"/>
     </x:row>
     <x:row r="419">
       <x:c r="B419" s="10"/>
       <x:c r="D419" s="10"/>
+      <x:c r="H419" s="11"/>
     </x:row>
     <x:row r="420">
       <x:c r="B420" s="10"/>
       <x:c r="D420" s="10"/>
+      <x:c r="H420" s="11"/>
     </x:row>
     <x:row r="421">
       <x:c r="B421" s="10"/>
       <x:c r="D421" s="10"/>
+      <x:c r="H421" s="11"/>
     </x:row>
     <x:row r="422">
       <x:c r="B422" s="10"/>
       <x:c r="D422" s="10"/>
+      <x:c r="H422" s="11"/>
     </x:row>
     <x:row r="423">
       <x:c r="B423" s="10"/>
       <x:c r="D423" s="10"/>
+      <x:c r="H423" s="11"/>
     </x:row>
     <x:row r="424">
       <x:c r="B424" s="10"/>
       <x:c r="D424" s="10"/>
+      <x:c r="H424" s="11"/>
     </x:row>
     <x:row r="425">
       <x:c r="B425" s="10"/>
       <x:c r="D425" s="10"/>
+      <x:c r="H425" s="11"/>
     </x:row>
     <x:row r="426">
       <x:c r="B426" s="10"/>
       <x:c r="D426" s="10"/>
+      <x:c r="H426" s="11"/>
     </x:row>
     <x:row r="427">
       <x:c r="B427" s="10"/>
       <x:c r="D427" s="10"/>
+      <x:c r="H427" s="11"/>
     </x:row>
     <x:row r="428">
       <x:c r="B428" s="10"/>
       <x:c r="D428" s="10"/>
+      <x:c r="H428" s="11"/>
     </x:row>
     <x:row r="429">
       <x:c r="B429" s="10"/>
       <x:c r="D429" s="10"/>
+      <x:c r="H429" s="11"/>
     </x:row>
     <x:row r="430">
       <x:c r="B430" s="10"/>
       <x:c r="D430" s="10"/>
+      <x:c r="H430" s="11"/>
     </x:row>
     <x:row r="431">
       <x:c r="B431" s="10"/>
       <x:c r="D431" s="10"/>
+      <x:c r="H431" s="11"/>
     </x:row>
     <x:row r="432">
       <x:c r="B432" s="10"/>
       <x:c r="D432" s="10"/>
+      <x:c r="H432" s="11"/>
     </x:row>
     <x:row r="433">
       <x:c r="B433" s="10"/>
       <x:c r="D433" s="10"/>
+      <x:c r="H433" s="11"/>
     </x:row>
     <x:row r="434">
       <x:c r="B434" s="10"/>
       <x:c r="D434" s="10"/>
+      <x:c r="H434" s="11"/>
     </x:row>
     <x:row r="435">
       <x:c r="B435" s="10"/>
       <x:c r="D435" s="10"/>
+      <x:c r="H435" s="11"/>
     </x:row>
     <x:row r="436">
       <x:c r="B436" s="10"/>
       <x:c r="D436" s="10"/>
+      <x:c r="H436" s="11"/>
     </x:row>
     <x:row r="437">
       <x:c r="B437" s="10"/>
       <x:c r="D437" s="10"/>
+      <x:c r="H437" s="11"/>
     </x:row>
     <x:row r="438">
       <x:c r="B438" s="10"/>
       <x:c r="D438" s="10"/>
+      <x:c r="H438" s="11"/>
     </x:row>
     <x:row r="439">
       <x:c r="B439" s="10"/>
       <x:c r="D439" s="10"/>
+      <x:c r="H439" s="11"/>
     </x:row>
     <x:row r="440">
       <x:c r="B440" s="10"/>
       <x:c r="D440" s="10"/>
+      <x:c r="H440" s="11"/>
     </x:row>
     <x:row r="441">
       <x:c r="B441" s="10"/>
       <x:c r="D441" s="10"/>
+      <x:c r="H441" s="11"/>
     </x:row>
     <x:row r="442">
       <x:c r="B442" s="10"/>
       <x:c r="D442" s="10"/>
+      <x:c r="H442" s="11"/>
     </x:row>
     <x:row r="443">
       <x:c r="B443" s="10"/>
       <x:c r="D443" s="10"/>
+      <x:c r="H443" s="11"/>
     </x:row>
     <x:row r="444">
       <x:c r="B444" s="10"/>
       <x:c r="D444" s="10"/>
+      <x:c r="H444" s="11"/>
     </x:row>
     <x:row r="445">
       <x:c r="B445" s="10"/>
       <x:c r="D445" s="10"/>
+      <x:c r="H445" s="11"/>
     </x:row>
     <x:row r="446">
       <x:c r="B446" s="10"/>
       <x:c r="D446" s="10"/>
+      <x:c r="H446" s="11"/>
     </x:row>
     <x:row r="447">
       <x:c r="B447" s="10"/>
       <x:c r="D447" s="10"/>
+      <x:c r="H447" s="11"/>
     </x:row>
     <x:row r="448">
       <x:c r="B448" s="10"/>
       <x:c r="D448" s="10"/>
+      <x:c r="H448" s="11"/>
     </x:row>
     <x:row r="449">
       <x:c r="B449" s="10"/>
       <x:c r="D449" s="10"/>
+      <x:c r="H449" s="11"/>
     </x:row>
     <x:row r="450">
       <x:c r="B450" s="10"/>
       <x:c r="D450" s="10"/>
+      <x:c r="H450" s="11"/>
     </x:row>
     <x:row r="451">
       <x:c r="B451" s="10"/>
       <x:c r="D451" s="10"/>
+      <x:c r="H451" s="11"/>
     </x:row>
     <x:row r="452">
       <x:c r="B452" s="10"/>
       <x:c r="D452" s="10"/>
+      <x:c r="H452" s="11"/>
     </x:row>
     <x:row r="453">
       <x:c r="B453" s="10"/>
       <x:c r="D453" s="10"/>
+      <x:c r="H453" s="11"/>
     </x:row>
     <x:row r="454">
       <x:c r="B454" s="10"/>
       <x:c r="D454" s="10"/>
+      <x:c r="H454" s="11"/>
     </x:row>
     <x:row r="455">
       <x:c r="B455" s="10"/>
       <x:c r="D455" s="10"/>
+      <x:c r="H455" s="11"/>
     </x:row>
     <x:row r="456">
       <x:c r="B456" s="10"/>
       <x:c r="D456" s="10"/>
+      <x:c r="H456" s="11"/>
     </x:row>
     <x:row r="457">
       <x:c r="B457" s="10"/>
       <x:c r="D457" s="10"/>
+      <x:c r="H457" s="11"/>
     </x:row>
     <x:row r="458">
       <x:c r="B458" s="10"/>
       <x:c r="D458" s="10"/>
+      <x:c r="H458" s="11"/>
     </x:row>
     <x:row r="459">
       <x:c r="B459" s="10"/>
       <x:c r="D459" s="10"/>
+      <x:c r="H459" s="11"/>
     </x:row>
     <x:row r="460">
       <x:c r="B460" s="10"/>
       <x:c r="D460" s="10"/>
+      <x:c r="H460" s="11"/>
     </x:row>
     <x:row r="461">
       <x:c r="B461" s="10"/>
       <x:c r="D461" s="10"/>
+      <x:c r="H461" s="11"/>
     </x:row>
     <x:row r="462">
       <x:c r="B462" s="10"/>
       <x:c r="D462" s="10"/>
+      <x:c r="H462" s="11"/>
     </x:row>
     <x:row r="463">
       <x:c r="B463" s="10"/>
       <x:c r="D463" s="10"/>
+      <x:c r="H463" s="11"/>
     </x:row>
     <x:row r="464">
       <x:c r="B464" s="10"/>
       <x:c r="D464" s="10"/>
+      <x:c r="H464" s="11"/>
     </x:row>
     <x:row r="465">
       <x:c r="B465" s="10"/>
       <x:c r="D465" s="10"/>
+      <x:c r="H465" s="11"/>
     </x:row>
     <x:row r="466">
       <x:c r="B466" s="10"/>
       <x:c r="D466" s="10"/>
+      <x:c r="H466" s="11"/>
     </x:row>
     <x:row r="467">
       <x:c r="B467" s="10"/>
       <x:c r="D467" s="10"/>
+      <x:c r="H467" s="11"/>
     </x:row>
     <x:row r="468">
       <x:c r="B468" s="10"/>
       <x:c r="D468" s="10"/>
+      <x:c r="H468" s="11"/>
     </x:row>
     <x:row r="469">
       <x:c r="B469" s="10"/>
       <x:c r="D469" s="10"/>
+      <x:c r="H469" s="11"/>
     </x:row>
     <x:row r="470">
       <x:c r="B470" s="10"/>
       <x:c r="D470" s="10"/>
+      <x:c r="H470" s="11"/>
     </x:row>
     <x:row r="471">
       <x:c r="B471" s="10"/>
       <x:c r="D471" s="10"/>
+      <x:c r="H471" s="11"/>
     </x:row>
     <x:row r="472">
       <x:c r="B472" s="10"/>
       <x:c r="D472" s="10"/>
+      <x:c r="H472" s="11"/>
     </x:row>
     <x:row r="473">
       <x:c r="B473" s="10"/>
       <x:c r="D473" s="10"/>
+      <x:c r="H473" s="11"/>
     </x:row>
     <x:row r="474">
       <x:c r="B474" s="10"/>
       <x:c r="D474" s="10"/>
+      <x:c r="H474" s="11"/>
     </x:row>
     <x:row r="475">
       <x:c r="B475" s="10"/>
       <x:c r="D475" s="10"/>
+      <x:c r="H475" s="11"/>
     </x:row>
     <x:row r="476">
       <x:c r="B476" s="10"/>
       <x:c r="D476" s="10"/>
+      <x:c r="H476" s="11"/>
     </x:row>
     <x:row r="477">
       <x:c r="B477" s="10"/>
       <x:c r="D477" s="10"/>
+      <x:c r="H477" s="11"/>
     </x:row>
     <x:row r="478">
       <x:c r="B478" s="10"/>
       <x:c r="D478" s="10"/>
+      <x:c r="H478" s="11"/>
     </x:row>
     <x:row r="479">
       <x:c r="B479" s="10"/>
       <x:c r="D479" s="10"/>
+      <x:c r="H479" s="11"/>
     </x:row>
     <x:row r="480">
       <x:c r="B480" s="10"/>
       <x:c r="D480" s="10"/>
+      <x:c r="H480" s="11"/>
     </x:row>
     <x:row r="481">
       <x:c r="B481" s="10"/>
       <x:c r="D481" s="10"/>
+      <x:c r="H481" s="11"/>
     </x:row>
     <x:row r="482">
       <x:c r="B482" s="10"/>
       <x:c r="D482" s="10"/>
+      <x:c r="H482" s="11"/>
     </x:row>
     <x:row r="483">
       <x:c r="B483" s="10"/>
       <x:c r="D483" s="10"/>
+      <x:c r="H483" s="11"/>
     </x:row>
     <x:row r="484">
       <x:c r="B484" s="10"/>
       <x:c r="D484" s="10"/>
+      <x:c r="H484" s="11"/>
     </x:row>
     <x:row r="485">
       <x:c r="B485" s="10"/>
       <x:c r="D485" s="10"/>
+      <x:c r="H485" s="11"/>
     </x:row>
     <x:row r="486">
       <x:c r="B486" s="10"/>
       <x:c r="D486" s="10"/>
+      <x:c r="H486" s="11"/>
     </x:row>
     <x:row r="487">
       <x:c r="B487" s="10"/>
       <x:c r="D487" s="10"/>
+      <x:c r="H487" s="11"/>
     </x:row>
     <x:row r="488">
       <x:c r="B488" s="10"/>
       <x:c r="D488" s="10"/>
+      <x:c r="H488" s="11"/>
     </x:row>
     <x:row r="489">
       <x:c r="B489" s="10"/>
       <x:c r="D489" s="10"/>
+      <x:c r="H489" s="11"/>
     </x:row>
     <x:row r="490">
       <x:c r="B490" s="10"/>
       <x:c r="D490" s="10"/>
+      <x:c r="H490" s="11"/>
     </x:row>
     <x:row r="491">
       <x:c r="B491" s="10"/>
       <x:c r="D491" s="10"/>
+      <x:c r="H491" s="11"/>
     </x:row>
     <x:row r="492">
       <x:c r="B492" s="10"/>
       <x:c r="D492" s="10"/>
+      <x:c r="H492" s="11"/>
     </x:row>
     <x:row r="493">
       <x:c r="B493" s="10"/>
       <x:c r="D493" s="10"/>
+      <x:c r="H493" s="11"/>
     </x:row>
     <x:row r="494">
       <x:c r="B494" s="10"/>
       <x:c r="D494" s="10"/>
+      <x:c r="H494" s="11"/>
     </x:row>
     <x:row r="495">
       <x:c r="B495" s="10"/>
       <x:c r="D495" s="10"/>
+      <x:c r="H495" s="11"/>
     </x:row>
     <x:row r="496">
       <x:c r="B496" s="10"/>
       <x:c r="D496" s="10"/>
+      <x:c r="H496" s="11"/>
     </x:row>
     <x:row r="497">
       <x:c r="B497" s="10"/>
       <x:c r="D497" s="10"/>
+      <x:c r="H497" s="11"/>
     </x:row>
     <x:row r="498">
       <x:c r="B498" s="10"/>
       <x:c r="D498" s="10"/>
+      <x:c r="H498" s="11"/>
     </x:row>
     <x:row r="499">
       <x:c r="B499" s="10"/>
       <x:c r="D499" s="10"/>
+      <x:c r="H499" s="11"/>
     </x:row>
     <x:row r="500">
       <x:c r="B500" s="10"/>
       <x:c r="D500" s="10"/>
+      <x:c r="H500" s="11"/>
     </x:row>
     <x:row r="501">
       <x:c r="B501" s="10"/>
       <x:c r="D501" s="10"/>
+      <x:c r="H501" s="11"/>
     </x:row>
     <x:row r="502">
       <x:c r="B502" s="10"/>
       <x:c r="D502" s="10"/>
+      <x:c r="H502" s="11"/>
     </x:row>
     <x:row r="503">
       <x:c r="B503" s="10"/>
       <x:c r="D503" s="10"/>
+      <x:c r="H503" s="11"/>
     </x:row>
     <x:row r="504">
       <x:c r="B504" s="10"/>
       <x:c r="D504" s="10"/>
+      <x:c r="H504" s="11"/>
     </x:row>
     <x:row r="505">
       <x:c r="B505" s="10"/>
       <x:c r="D505" s="10"/>
+      <x:c r="H505" s="11"/>
     </x:row>
     <x:row r="506">
       <x:c r="B506" s="10"/>
       <x:c r="D506" s="10"/>
+      <x:c r="H506" s="11"/>
     </x:row>
     <x:row r="507">
       <x:c r="B507" s="10"/>
       <x:c r="D507" s="10"/>
+      <x:c r="H507" s="11"/>
     </x:row>
     <x:row r="508">
       <x:c r="B508" s="10"/>
       <x:c r="D508" s="10"/>
+      <x:c r="H508" s="11"/>
     </x:row>
     <x:row r="509">
       <x:c r="B509" s="10"/>
       <x:c r="D509" s="10"/>
+      <x:c r="H509" s="11"/>
     </x:row>
     <x:row r="510">
       <x:c r="B510" s="10"/>
       <x:c r="D510" s="10"/>
+      <x:c r="H510" s="11"/>
     </x:row>
     <x:row r="511">
       <x:c r="B511" s="10"/>
       <x:c r="D511" s="10"/>
+      <x:c r="H511" s="11"/>
     </x:row>
     <x:row r="512">
       <x:c r="B512" s="10"/>
       <x:c r="D512" s="10"/>
+      <x:c r="H512" s="11"/>
     </x:row>
     <x:row r="513">
       <x:c r="B513" s="10"/>
       <x:c r="D513" s="10"/>
+      <x:c r="H513" s="11"/>
     </x:row>
     <x:row r="514">
       <x:c r="B514" s="10"/>
       <x:c r="D514" s="10"/>
+      <x:c r="H514" s="11"/>
     </x:row>
     <x:row r="515">
       <x:c r="B515" s="10"/>
       <x:c r="D515" s="10"/>
+      <x:c r="H515" s="11"/>
     </x:row>
     <x:row r="516">
       <x:c r="B516" s="10"/>
       <x:c r="D516" s="10"/>
+      <x:c r="H516" s="11"/>
     </x:row>
     <x:row r="517">
       <x:c r="B517" s="10"/>
       <x:c r="D517" s="10"/>
+      <x:c r="H517" s="11"/>
     </x:row>
     <x:row r="518">
       <x:c r="B518" s="10"/>
       <x:c r="D518" s="10"/>
+      <x:c r="H518" s="11"/>
     </x:row>
     <x:row r="519">
       <x:c r="B519" s="10"/>
       <x:c r="D519" s="10"/>
+      <x:c r="H519" s="11"/>
     </x:row>
     <x:row r="520">
       <x:c r="B520" s="10"/>
       <x:c r="D520" s="10"/>
+      <x:c r="H520" s="11"/>
     </x:row>
     <x:row r="521">
       <x:c r="B521" s="10"/>
       <x:c r="D521" s="10"/>
+      <x:c r="H521" s="11"/>
     </x:row>
     <x:row r="522">
       <x:c r="B522" s="10"/>
       <x:c r="D522" s="10"/>
+      <x:c r="H522" s="11"/>
     </x:row>
     <x:row r="523">
       <x:c r="B523" s="10"/>
       <x:c r="D523" s="10"/>
+      <x:c r="H523" s="11"/>
     </x:row>
     <x:row r="524">
       <x:c r="B524" s="10"/>
       <x:c r="D524" s="10"/>
+      <x:c r="H524" s="11"/>
     </x:row>
     <x:row r="525">
       <x:c r="B525" s="10"/>
       <x:c r="D525" s="10"/>
+      <x:c r="H525" s="11"/>
     </x:row>
     <x:row r="526">
       <x:c r="B526" s="10"/>
       <x:c r="D526" s="10"/>
+      <x:c r="H526" s="11"/>
     </x:row>
     <x:row r="527">
       <x:c r="B527" s="10"/>
       <x:c r="D527" s="10"/>
+      <x:c r="H527" s="11"/>
     </x:row>
     <x:row r="528">
       <x:c r="B528" s="10"/>
       <x:c r="D528" s="10"/>
+      <x:c r="H528" s="11"/>
     </x:row>
     <x:row r="529">
       <x:c r="B529" s="10"/>
       <x:c r="D529" s="10"/>
+      <x:c r="H529" s="11"/>
     </x:row>
     <x:row r="530">
       <x:c r="B530" s="10"/>
       <x:c r="D530" s="10"/>
+      <x:c r="H530" s="11"/>
     </x:row>
     <x:row r="531">
       <x:c r="B531" s="10"/>
       <x:c r="D531" s="10"/>
+      <x:c r="H531" s="11"/>
     </x:row>
     <x:row r="532">
       <x:c r="B532" s="10"/>
       <x:c r="D532" s="10"/>
+      <x:c r="H532" s="11"/>
     </x:row>
     <x:row r="533">
       <x:c r="B533" s="10"/>
       <x:c r="D533" s="10"/>
+      <x:c r="H533" s="11"/>
     </x:row>
     <x:row r="534">
       <x:c r="B534" s="10"/>
       <x:c r="D534" s="10"/>
+      <x:c r="H534" s="11"/>
     </x:row>
     <x:row r="535">
       <x:c r="B535" s="10"/>
       <x:c r="D535" s="10"/>
+      <x:c r="H535" s="11"/>
     </x:row>
     <x:row r="536">
       <x:c r="B536" s="10"/>
       <x:c r="D536" s="10"/>
+      <x:c r="H536" s="11"/>
     </x:row>
     <x:row r="537">
       <x:c r="B537" s="10"/>
       <x:c r="D537" s="10"/>
+      <x:c r="H537" s="11"/>
     </x:row>
     <x:row r="538">
       <x:c r="B538" s="10"/>
       <x:c r="D538" s="10"/>
+      <x:c r="H538" s="11"/>
     </x:row>
     <x:row r="539">
       <x:c r="B539" s="10"/>
       <x:c r="D539" s="10"/>
+      <x:c r="H539" s="11"/>
     </x:row>
     <x:row r="540">
       <x:c r="B540" s="10"/>
       <x:c r="D540" s="10"/>
+      <x:c r="H540" s="11"/>
     </x:row>
     <x:row r="541">
       <x:c r="B541" s="10"/>
       <x:c r="D541" s="10"/>
+      <x:c r="H541" s="11"/>
     </x:row>
     <x:row r="542">
       <x:c r="B542" s="10"/>
       <x:c r="D542" s="10"/>
+      <x:c r="H542" s="11"/>
     </x:row>
     <x:row r="543">
       <x:c r="B543" s="10"/>
       <x:c r="D543" s="10"/>
+      <x:c r="H543" s="11"/>
     </x:row>
     <x:row r="544">
       <x:c r="B544" s="10"/>
       <x:c r="D544" s="10"/>
+      <x:c r="H544" s="11"/>
     </x:row>
     <x:row r="545">
       <x:c r="B545" s="10"/>
       <x:c r="D545" s="10"/>
+      <x:c r="H545" s="11"/>
     </x:row>
     <x:row r="546">
       <x:c r="B546" s="10"/>
       <x:c r="D546" s="10"/>
+      <x:c r="H546" s="11"/>
     </x:row>
     <x:row r="547">
       <x:c r="B547" s="10"/>
       <x:c r="D547" s="10"/>
+      <x:c r="H547" s="11"/>
     </x:row>
     <x:row r="548">
       <x:c r="B548" s="10"/>
       <x:c r="D548" s="10"/>
+      <x:c r="H548" s="11"/>
     </x:row>
     <x:row r="549">
       <x:c r="B549" s="10"/>
       <x:c r="D549" s="10"/>
+      <x:c r="H549" s="11"/>
     </x:row>
     <x:row r="550">
       <x:c r="B550" s="10"/>
       <x:c r="D550" s="10"/>
+      <x:c r="H550" s="11"/>
     </x:row>
     <x:row r="551">
       <x:c r="B551" s="10"/>
       <x:c r="D551" s="10"/>
+      <x:c r="H551" s="11"/>
     </x:row>
     <x:row r="552">
       <x:c r="B552" s="10"/>
       <x:c r="D552" s="10"/>
+      <x:c r="H552" s="11"/>
     </x:row>
     <x:row r="553">
       <x:c r="B553" s="10"/>
       <x:c r="D553" s="10"/>
+      <x:c r="H553" s="11"/>
     </x:row>
     <x:row r="554">
       <x:c r="B554" s="10"/>
       <x:c r="D554" s="10"/>
+      <x:c r="H554" s="11"/>
     </x:row>
     <x:row r="555">
       <x:c r="B555" s="10"/>
       <x:c r="D555" s="10"/>
+      <x:c r="H555" s="11"/>
     </x:row>
     <x:row r="556">
       <x:c r="B556" s="10"/>
       <x:c r="D556" s="10"/>
+      <x:c r="H556" s="11"/>
     </x:row>
     <x:row r="557">
       <x:c r="B557" s="10"/>
       <x:c r="D557" s="10"/>
+      <x:c r="H557" s="11"/>
     </x:row>
     <x:row r="558">
       <x:c r="B558" s="10"/>
       <x:c r="D558" s="10"/>
+      <x:c r="H558" s="11"/>
     </x:row>
     <x:row r="559">
       <x:c r="B559" s="10"/>
       <x:c r="D559" s="10"/>
+      <x:c r="H559" s="11"/>
     </x:row>
     <x:row r="560">
       <x:c r="B560" s="10"/>
       <x:c r="D560" s="10"/>
+      <x:c r="H560" s="11"/>
     </x:row>
     <x:row r="561">
       <x:c r="B561" s="10"/>
       <x:c r="D561" s="10"/>
+      <x:c r="H561" s="11"/>
     </x:row>
     <x:row r="562">
       <x:c r="B562" s="10"/>
       <x:c r="D562" s="10"/>
+      <x:c r="H562" s="11"/>
     </x:row>
     <x:row r="563">
       <x:c r="B563" s="10"/>
       <x:c r="D563" s="10"/>
+      <x:c r="H563" s="11"/>
     </x:row>
     <x:row r="564">
       <x:c r="B564" s="10"/>
       <x:c r="D564" s="10"/>
+      <x:c r="H564" s="11"/>
     </x:row>
     <x:row r="565">
       <x:c r="B565" s="10"/>
       <x:c r="D565" s="10"/>
+      <x:c r="H565" s="11"/>
     </x:row>
     <x:row r="566">
       <x:c r="B566" s="10"/>
       <x:c r="D566" s="10"/>
+      <x:c r="H566" s="11"/>
     </x:row>
     <x:row r="567">
       <x:c r="B567" s="10"/>
       <x:c r="D567" s="10"/>
+      <x:c r="H567" s="11"/>
     </x:row>
     <x:row r="568">
       <x:c r="B568" s="10"/>
       <x:c r="D568" s="10"/>
+      <x:c r="H568" s="11"/>
     </x:row>
     <x:row r="569">
       <x:c r="B569" s="10"/>
       <x:c r="D569" s="10"/>
+      <x:c r="H569" s="11"/>
     </x:row>
     <x:row r="570">
       <x:c r="B570" s="10"/>
       <x:c r="D570" s="10"/>
+      <x:c r="H570" s="11"/>
     </x:row>
     <x:row r="571">
       <x:c r="B571" s="10"/>
       <x:c r="D571" s="10"/>
+      <x:c r="H571" s="11"/>
     </x:row>
     <x:row r="572">
       <x:c r="B572" s="10"/>
       <x:c r="D572" s="10"/>
+      <x:c r="H572" s="11"/>
     </x:row>
     <x:row r="573">
       <x:c r="B573" s="10"/>
       <x:c r="D573" s="10"/>
+      <x:c r="H573" s="11"/>
     </x:row>
     <x:row r="574">
       <x:c r="B574" s="10"/>
       <x:c r="D574" s="10"/>
+      <x:c r="H574" s="11"/>
     </x:row>
     <x:row r="575">
       <x:c r="B575" s="10"/>
       <x:c r="D575" s="10"/>
+      <x:c r="H575" s="11"/>
     </x:row>
     <x:row r="576">
       <x:c r="B576" s="10"/>
       <x:c r="D576" s="10"/>
+      <x:c r="H576" s="11"/>
     </x:row>
     <x:row r="577">
       <x:c r="B577" s="10"/>
       <x:c r="D577" s="10"/>
+      <x:c r="H577" s="11"/>
     </x:row>
     <x:row r="578">
       <x:c r="B578" s="10"/>
       <x:c r="D578" s="10"/>
+      <x:c r="H578" s="11"/>
     </x:row>
     <x:row r="579">
       <x:c r="B579" s="10"/>
       <x:c r="D579" s="10"/>
+      <x:c r="H579" s="11"/>
     </x:row>
     <x:row r="580">
       <x:c r="B580" s="10"/>
       <x:c r="D580" s="10"/>
+      <x:c r="H580" s="11"/>
     </x:row>
     <x:row r="581">
       <x:c r="B581" s="10"/>
       <x:c r="D581" s="10"/>
+      <x:c r="H581" s="11"/>
     </x:row>
     <x:row r="582">
       <x:c r="B582" s="10"/>
       <x:c r="D582" s="10"/>
+      <x:c r="H582" s="11"/>
     </x:row>
     <x:row r="583">
       <x:c r="B583" s="10"/>
       <x:c r="D583" s="10"/>
+      <x:c r="H583" s="11"/>
     </x:row>
     <x:row r="584">
       <x:c r="B584" s="10"/>
       <x:c r="D584" s="10"/>
+      <x:c r="H584" s="11"/>
     </x:row>
     <x:row r="585">
       <x:c r="B585" s="10"/>
       <x:c r="D585" s="10"/>
+      <x:c r="H585" s="11"/>
     </x:row>
     <x:row r="586">
       <x:c r="B586" s="10"/>
       <x:c r="D586" s="10"/>
+      <x:c r="H586" s="11"/>
     </x:row>
     <x:row r="587">
       <x:c r="B587" s="10"/>
       <x:c r="D587" s="10"/>
+      <x:c r="H587" s="11"/>
     </x:row>
     <x:row r="588">
       <x:c r="B588" s="10"/>
       <x:c r="D588" s="10"/>
+      <x:c r="H588" s="11"/>
     </x:row>
     <x:row r="589">
       <x:c r="B589" s="10"/>
       <x:c r="D589" s="10"/>
+      <x:c r="H589" s="11"/>
     </x:row>
     <x:row r="590">
       <x:c r="B590" s="10"/>
       <x:c r="D590" s="10"/>
+      <x:c r="H590" s="11"/>
     </x:row>
     <x:row r="591">
       <x:c r="B591" s="10"/>
       <x:c r="D591" s="10"/>
+      <x:c r="H591" s="11"/>
     </x:row>
     <x:row r="592">
       <x:c r="B592" s="10"/>
       <x:c r="D592" s="10"/>
+      <x:c r="H592" s="11"/>
     </x:row>
     <x:row r="593">
       <x:c r="B593" s="10"/>
       <x:c r="D593" s="10"/>
+      <x:c r="H593" s="11"/>
     </x:row>
     <x:row r="594">
       <x:c r="B594" s="10"/>
       <x:c r="D594" s="10"/>
+      <x:c r="H594" s="11"/>
     </x:row>
     <x:row r="595">
       <x:c r="B595" s="10"/>
       <x:c r="D595" s="10"/>
+      <x:c r="H595" s="11"/>
     </x:row>
     <x:row r="596">
       <x:c r="B596" s="10"/>
       <x:c r="D596" s="10"/>
+      <x:c r="H596" s="11"/>
     </x:row>
     <x:row r="597">
       <x:c r="B597" s="10"/>
       <x:c r="D597" s="10"/>
+      <x:c r="H597" s="11"/>
     </x:row>
     <x:row r="598">
       <x:c r="B598" s="10"/>
       <x:c r="D598" s="10"/>
+      <x:c r="H598" s="11"/>
     </x:row>
     <x:row r="599">
       <x:c r="B599" s="10"/>
       <x:c r="D599" s="10"/>
+      <x:c r="H599" s="11"/>
     </x:row>
     <x:row r="600">
       <x:c r="B600" s="10"/>
       <x:c r="D600" s="10"/>
+      <x:c r="H600" s="11"/>
     </x:row>
     <x:row r="601">
       <x:c r="B601" s="10"/>
       <x:c r="D601" s="10"/>
+      <x:c r="H601" s="11"/>
     </x:row>
     <x:row r="602">
       <x:c r="B602" s="10"/>
       <x:c r="D602" s="10"/>
+      <x:c r="H602" s="11"/>
     </x:row>
     <x:row r="603">
       <x:c r="B603" s="10"/>
       <x:c r="D603" s="10"/>
+      <x:c r="H603" s="11"/>
     </x:row>
     <x:row r="604">
       <x:c r="B604" s="10"/>
       <x:c r="D604" s="10"/>
+      <x:c r="H604" s="11"/>
     </x:row>
     <x:row r="605">
       <x:c r="B605" s="10"/>
       <x:c r="D605" s="10"/>
+      <x:c r="H605" s="11"/>
     </x:row>
     <x:row r="606">
       <x:c r="B606" s="10"/>
       <x:c r="D606" s="10"/>
+      <x:c r="H606" s="11"/>
     </x:row>
     <x:row r="607">
       <x:c r="B607" s="10"/>
       <x:c r="D607" s="10"/>
+      <x:c r="H607" s="11"/>
     </x:row>
     <x:row r="608">
       <x:c r="B608" s="10"/>
       <x:c r="D608" s="10"/>
+      <x:c r="H608" s="11"/>
     </x:row>
     <x:row r="609">
       <x:c r="B609" s="10"/>
       <x:c r="D609" s="10"/>
+      <x:c r="H609" s="11"/>
     </x:row>
     <x:row r="610">
       <x:c r="B610" s="10"/>
       <x:c r="D610" s="10"/>
+      <x:c r="H610" s="11"/>
     </x:row>
     <x:row r="611">
       <x:c r="B611" s="10"/>
       <x:c r="D611" s="10"/>
+      <x:c r="H611" s="11"/>
     </x:row>
     <x:row r="612">
       <x:c r="B612" s="10"/>
       <x:c r="D612" s="10"/>
+      <x:c r="H612" s="11"/>
     </x:row>
     <x:row r="613">
       <x:c r="B613" s="10"/>
       <x:c r="D613" s="10"/>
+      <x:c r="H613" s="11"/>
     </x:row>
     <x:row r="614">
       <x:c r="B614" s="10"/>
       <x:c r="D614" s="10"/>
+      <x:c r="H614" s="11"/>
     </x:row>
     <x:row r="615">
       <x:c r="B615" s="10"/>
       <x:c r="D615" s="10"/>
+      <x:c r="H615" s="11"/>
     </x:row>
     <x:row r="616">
       <x:c r="B616" s="10"/>
       <x:c r="D616" s="10"/>
+      <x:c r="H616" s="11"/>
     </x:row>
     <x:row r="617">
       <x:c r="B617" s="10"/>
       <x:c r="D617" s="10"/>
+      <x:c r="H617" s="11"/>
     </x:row>
     <x:row r="618">
       <x:c r="B618" s="10"/>
       <x:c r="D618" s="10"/>
+      <x:c r="H618" s="11"/>
     </x:row>
     <x:row r="619">
       <x:c r="B619" s="10"/>
       <x:c r="D619" s="10"/>
+      <x:c r="H619" s="11"/>
     </x:row>
     <x:row r="620">
       <x:c r="B620" s="10"/>
       <x:c r="D620" s="10"/>
+      <x:c r="H620" s="11"/>
     </x:row>
     <x:row r="621">
       <x:c r="B621" s="10"/>
       <x:c r="D621" s="10"/>
+      <x:c r="H621" s="11"/>
     </x:row>
     <x:row r="622">
       <x:c r="B622" s="10"/>
       <x:c r="D622" s="10"/>
+      <x:c r="H622" s="11"/>
     </x:row>
     <x:row r="623">
       <x:c r="B623" s="10"/>
       <x:c r="D623" s="10"/>
+      <x:c r="H623" s="11"/>
     </x:row>
     <x:row r="624">
       <x:c r="B624" s="10"/>
       <x:c r="D624" s="10"/>
+      <x:c r="H624" s="11"/>
     </x:row>
     <x:row r="625">
       <x:c r="B625" s="10"/>
       <x:c r="D625" s="10"/>
+      <x:c r="H625" s="11"/>
     </x:row>
     <x:row r="626">
       <x:c r="B626" s="10"/>
       <x:c r="D626" s="10"/>
+      <x:c r="H626" s="11"/>
     </x:row>
     <x:row r="627">
       <x:c r="B627" s="10"/>
       <x:c r="D627" s="10"/>
+      <x:c r="H627" s="11"/>
     </x:row>
     <x:row r="628">
       <x:c r="B628" s="10"/>
       <x:c r="D628" s="10"/>
+      <x:c r="H628" s="11"/>
     </x:row>
     <x:row r="629">
       <x:c r="B629" s="10"/>
       <x:c r="D629" s="10"/>
+      <x:c r="H629" s="11"/>
     </x:row>
     <x:row r="630">
       <x:c r="B630" s="10"/>
       <x:c r="D630" s="10"/>
+      <x:c r="H630" s="11"/>
     </x:row>
     <x:row r="631">
       <x:c r="B631" s="10"/>
       <x:c r="D631" s="10"/>
+      <x:c r="H631" s="11"/>
     </x:row>
     <x:row r="632">
       <x:c r="B632" s="10"/>
       <x:c r="D632" s="10"/>
+      <x:c r="H632" s="11"/>
     </x:row>
     <x:row r="633">
       <x:c r="B633" s="10"/>
       <x:c r="D633" s="10"/>
+      <x:c r="H633" s="11"/>
     </x:row>
     <x:row r="634">
       <x:c r="B634" s="10"/>
       <x:c r="D634" s="10"/>
+      <x:c r="H634" s="11"/>
     </x:row>
     <x:row r="635">
       <x:c r="B635" s="10"/>
       <x:c r="D635" s="10"/>
+      <x:c r="H635" s="11"/>
     </x:row>
     <x:row r="636">
       <x:c r="B636" s="10"/>
       <x:c r="D636" s="10"/>
+      <x:c r="H636" s="11"/>
     </x:row>
     <x:row r="637">
       <x:c r="B637" s="10"/>
       <x:c r="D637" s="10"/>
+      <x:c r="H637" s="11"/>
     </x:row>
     <x:row r="638">
       <x:c r="B638" s="10"/>
       <x:c r="D638" s="10"/>
+      <x:c r="H638" s="11"/>
     </x:row>
     <x:row r="639">
       <x:c r="B639" s="10"/>
       <x:c r="D639" s="10"/>
+      <x:c r="H639" s="11"/>
     </x:row>
     <x:row r="640">
       <x:c r="B640" s="10"/>
       <x:c r="D640" s="10"/>
+      <x:c r="H640" s="11"/>
     </x:row>
     <x:row r="641">
       <x:c r="B641" s="10"/>
       <x:c r="D641" s="10"/>
+      <x:c r="H641" s="11"/>
     </x:row>
     <x:row r="642">
       <x:c r="B642" s="10"/>
       <x:c r="D642" s="10"/>
+      <x:c r="H642" s="11"/>
     </x:row>
     <x:row r="643">
       <x:c r="B643" s="10"/>
       <x:c r="D643" s="10"/>
+      <x:c r="H643" s="11"/>
     </x:row>
     <x:row r="644">
       <x:c r="B644" s="10"/>
       <x:c r="D644" s="10"/>
+      <x:c r="H644" s="11"/>
     </x:row>
     <x:row r="645">
       <x:c r="B645" s="10"/>
       <x:c r="D645" s="10"/>
+      <x:c r="H645" s="11"/>
     </x:row>
     <x:row r="646">
       <x:c r="B646" s="10"/>
       <x:c r="D646" s="10"/>
+      <x:c r="H646" s="11"/>
     </x:row>
     <x:row r="647">
       <x:c r="B647" s="10"/>
       <x:c r="D647" s="10"/>
+      <x:c r="H647" s="11"/>
     </x:row>
     <x:row r="648">
       <x:c r="B648" s="10"/>
       <x:c r="D648" s="10"/>
+      <x:c r="H648" s="11"/>
     </x:row>
     <x:row r="649">
       <x:c r="B649" s="10"/>
       <x:c r="D649" s="10"/>
+      <x:c r="H649" s="11"/>
     </x:row>
     <x:row r="650">
       <x:c r="B650" s="10"/>
       <x:c r="D650" s="10"/>
+      <x:c r="H650" s="11"/>
     </x:row>
     <x:row r="651">
       <x:c r="B651" s="10"/>
       <x:c r="D651" s="10"/>
+      <x:c r="H651" s="11"/>
     </x:row>
     <x:row r="652">
       <x:c r="B652" s="10"/>
       <x:c r="D652" s="10"/>
+      <x:c r="H652" s="11"/>
     </x:row>
     <x:row r="653">
       <x:c r="B653" s="10"/>
       <x:c r="D653" s="10"/>
+      <x:c r="H653" s="11"/>
     </x:row>
     <x:row r="654">
       <x:c r="B654" s="10"/>
       <x:c r="D654" s="10"/>
+      <x:c r="H654" s="11"/>
     </x:row>
     <x:row r="655">
       <x:c r="B655" s="10"/>
       <x:c r="D655" s="10"/>
+      <x:c r="H655" s="11"/>
     </x:row>
     <x:row r="656">
       <x:c r="B656" s="10"/>
       <x:c r="D656" s="10"/>
+      <x:c r="H656" s="11"/>
     </x:row>
     <x:row r="657">
       <x:c r="B657" s="10"/>
       <x:c r="D657" s="10"/>
+      <x:c r="H657" s="11"/>
     </x:row>
     <x:row r="658">
       <x:c r="B658" s="10"/>
       <x:c r="D658" s="10"/>
+      <x:c r="H658" s="11"/>
     </x:row>
     <x:row r="659">
       <x:c r="B659" s="10"/>
       <x:c r="D659" s="10"/>
+      <x:c r="H659" s="11"/>
     </x:row>
     <x:row r="660">
       <x:c r="B660" s="10"/>
       <x:c r="D660" s="10"/>
+      <x:c r="H660" s="11"/>
     </x:row>
     <x:row r="661">
       <x:c r="B661" s="10"/>
       <x:c r="D661" s="10"/>
+      <x:c r="H661" s="11"/>
     </x:row>
     <x:row r="662">
       <x:c r="B662" s="10"/>
       <x:c r="D662" s="10"/>
+      <x:c r="H662" s="11"/>
     </x:row>
     <x:row r="663">
       <x:c r="B663" s="10"/>
       <x:c r="D663" s="10"/>
+      <x:c r="H663" s="11"/>
     </x:row>
     <x:row r="664">
       <x:c r="B664" s="10"/>
       <x:c r="D664" s="10"/>
+      <x:c r="H664" s="11"/>
     </x:row>
     <x:row r="665">
       <x:c r="B665" s="10"/>
       <x:c r="D665" s="10"/>
+      <x:c r="H665" s="11"/>
     </x:row>
     <x:row r="666">
       <x:c r="B666" s="10"/>
       <x:c r="D666" s="10"/>
+      <x:c r="H666" s="11"/>
     </x:row>
     <x:row r="667">
       <x:c r="B667" s="10"/>
       <x:c r="D667" s="10"/>
+      <x:c r="H667" s="11"/>
     </x:row>
     <x:row r="668">
       <x:c r="B668" s="10"/>
       <x:c r="D668" s="10"/>
+      <x:c r="H668" s="11"/>
     </x:row>
     <x:row r="669">
       <x:c r="B669" s="10"/>
       <x:c r="D669" s="10"/>
+      <x:c r="H669" s="11"/>
     </x:row>
     <x:row r="670">
       <x:c r="B670" s="10"/>
       <x:c r="D670" s="10"/>
+      <x:c r="H670" s="11"/>
     </x:row>
     <x:row r="671">
       <x:c r="B671" s="10"/>
       <x:c r="D671" s="10"/>
+      <x:c r="H671" s="11"/>
     </x:row>
     <x:row r="672">
       <x:c r="B672" s="10"/>
       <x:c r="D672" s="10"/>
+      <x:c r="H672" s="11"/>
     </x:row>
     <x:row r="673">
       <x:c r="B673" s="10"/>
       <x:c r="D673" s="10"/>
+      <x:c r="H673" s="11"/>
     </x:row>
     <x:row r="674">
       <x:c r="B674" s="10"/>
       <x:c r="D674" s="10"/>
+      <x:c r="H674" s="11"/>
     </x:row>
     <x:row r="675">
       <x:c r="B675" s="10"/>
       <x:c r="D675" s="10"/>
+      <x:c r="H675" s="11"/>
     </x:row>
     <x:row r="676">
       <x:c r="B676" s="10"/>
       <x:c r="D676" s="10"/>
+      <x:c r="H676" s="11"/>
     </x:row>
     <x:row r="677">
       <x:c r="B677" s="10"/>
       <x:c r="D677" s="10"/>
+      <x:c r="H677" s="11"/>
     </x:row>
     <x:row r="678">
       <x:c r="B678" s="10"/>
       <x:c r="D678" s="10"/>
+      <x:c r="H678" s="11"/>
     </x:row>
     <x:row r="679">
       <x:c r="B679" s="10"/>
       <x:c r="D679" s="10"/>
+      <x:c r="H679" s="11"/>
     </x:row>
     <x:row r="680">
       <x:c r="B680" s="10"/>
       <x:c r="D680" s="10"/>
+      <x:c r="H680" s="11"/>
     </x:row>
     <x:row r="681">
       <x:c r="B681" s="10"/>
       <x:c r="D681" s="10"/>
+      <x:c r="H681" s="11"/>
     </x:row>
     <x:row r="682">
       <x:c r="B682" s="10"/>
       <x:c r="D682" s="10"/>
+      <x:c r="H682" s="11"/>
     </x:row>
     <x:row r="683">
       <x:c r="B683" s="10"/>
       <x:c r="D683" s="10"/>
+      <x:c r="H683" s="11"/>
     </x:row>
     <x:row r="684">
       <x:c r="B684" s="10"/>
       <x:c r="D684" s="10"/>
+      <x:c r="H684" s="11"/>
     </x:row>
     <x:row r="685">
       <x:c r="B685" s="10"/>
       <x:c r="D685" s="10"/>
+      <x:c r="H685" s="11"/>
     </x:row>
     <x:row r="686">
       <x:c r="B686" s="10"/>
       <x:c r="D686" s="10"/>
+      <x:c r="H686" s="11"/>
     </x:row>
     <x:row r="687">
       <x:c r="B687" s="10"/>
       <x:c r="D687" s="10"/>
+      <x:c r="H687" s="11"/>
     </x:row>
     <x:row r="688">
       <x:c r="B688" s="10"/>
       <x:c r="D688" s="10"/>
+      <x:c r="H688" s="11"/>
     </x:row>
     <x:row r="689">
       <x:c r="B689" s="10"/>
       <x:c r="D689" s="10"/>
+      <x:c r="H689" s="11"/>
     </x:row>
     <x:row r="690">
       <x:c r="B690" s="10"/>
       <x:c r="D690" s="10"/>
+      <x:c r="H690" s="11"/>
     </x:row>
     <x:row r="691">
       <x:c r="B691" s="10"/>
       <x:c r="D691" s="10"/>
+      <x:c r="H691" s="11"/>
     </x:row>
     <x:row r="692">
       <x:c r="B692" s="10"/>
       <x:c r="D692" s="10"/>
+      <x:c r="H692" s="11"/>
     </x:row>
     <x:row r="693">
       <x:c r="B693" s="10"/>
       <x:c r="D693" s="10"/>
+      <x:c r="H693" s="11"/>
     </x:row>
     <x:row r="694">
       <x:c r="B694" s="10"/>
       <x:c r="D694" s="10"/>
+      <x:c r="H694" s="11"/>
     </x:row>
     <x:row r="695">
       <x:c r="B695" s="10"/>
       <x:c r="D695" s="10"/>
+      <x:c r="H695" s="11"/>
     </x:row>
     <x:row r="696">
       <x:c r="B696" s="10"/>
       <x:c r="D696" s="10"/>
+      <x:c r="H696" s="11"/>
     </x:row>
     <x:row r="697">
       <x:c r="B697" s="10"/>
       <x:c r="D697" s="10"/>
+      <x:c r="H697" s="11"/>
     </x:row>
     <x:row r="698">
       <x:c r="B698" s="10"/>
       <x:c r="D698" s="10"/>
+      <x:c r="H698" s="11"/>
     </x:row>
     <x:row r="699">
       <x:c r="B699" s="10"/>
       <x:c r="D699" s="10"/>
+      <x:c r="H699" s="11"/>
     </x:row>
     <x:row r="700">
       <x:c r="B700" s="10"/>
       <x:c r="D700" s="10"/>
+      <x:c r="H700" s="11"/>
     </x:row>
     <x:row r="701">
       <x:c r="B701" s="10"/>
       <x:c r="D701" s="10"/>
+      <x:c r="H701" s="11"/>
     </x:row>
     <x:row r="702">
       <x:c r="B702" s="10"/>
       <x:c r="D702" s="10"/>
+      <x:c r="H702" s="11"/>
     </x:row>
     <x:row r="703">
       <x:c r="B703" s="10"/>
       <x:c r="D703" s="10"/>
+      <x:c r="H703" s="11"/>
     </x:row>
     <x:row r="704">
       <x:c r="B704" s="10"/>
       <x:c r="D704" s="10"/>
+      <x:c r="H704" s="11"/>
     </x:row>
     <x:row r="705">
       <x:c r="B705" s="10"/>
       <x:c r="D705" s="10"/>
+      <x:c r="H705" s="11"/>
     </x:row>
     <x:row r="706">
       <x:c r="B706" s="10"/>
       <x:c r="D706" s="10"/>
+      <x:c r="H706" s="11"/>
     </x:row>
     <x:row r="707">
       <x:c r="B707" s="10"/>
       <x:c r="D707" s="10"/>
+      <x:c r="H707" s="11"/>
     </x:row>
     <x:row r="708">
       <x:c r="B708" s="10"/>
       <x:c r="D708" s="10"/>
+      <x:c r="H708" s="11"/>
     </x:row>
     <x:row r="709">
       <x:c r="B709" s="10"/>
       <x:c r="D709" s="10"/>
+      <x:c r="H709" s="11"/>
     </x:row>
     <x:row r="710">
       <x:c r="B710" s="10"/>
       <x:c r="D710" s="10"/>
+      <x:c r="H710" s="11"/>
     </x:row>
     <x:row r="711">
       <x:c r="B711" s="10"/>
       <x:c r="D711" s="10"/>
+      <x:c r="H711" s="11"/>
     </x:row>
     <x:row r="712">
       <x:c r="B712" s="10"/>
       <x:c r="D712" s="10"/>
+      <x:c r="H712" s="11"/>
     </x:row>
     <x:row r="713">
       <x:c r="B713" s="10"/>
       <x:c r="D713" s="10"/>
+      <x:c r="H713" s="11"/>
     </x:row>
     <x:row r="714">
       <x:c r="B714" s="10"/>
       <x:c r="D714" s="10"/>
+      <x:c r="H714" s="11"/>
     </x:row>
     <x:row r="715">
       <x:c r="B715" s="10"/>
       <x:c r="D715" s="10"/>
+      <x:c r="H715" s="11"/>
     </x:row>
     <x:row r="716">
       <x:c r="B716" s="10"/>
       <x:c r="D716" s="10"/>
+      <x:c r="H716" s="11"/>
     </x:row>
     <x:row r="717">
       <x:c r="B717" s="10"/>
       <x:c r="D717" s="10"/>
+      <x:c r="H717" s="11"/>
     </x:row>
     <x:row r="718">
       <x:c r="B718" s="10"/>
       <x:c r="D718" s="10"/>
+      <x:c r="H718" s="11"/>
     </x:row>
     <x:row r="719">
       <x:c r="B719" s="10"/>
       <x:c r="D719" s="10"/>
+      <x:c r="H719" s="11"/>
     </x:row>
     <x:row r="720">
       <x:c r="B720" s="10"/>
       <x:c r="D720" s="10"/>
+      <x:c r="H720" s="11"/>
     </x:row>
     <x:row r="721">
       <x:c r="B721" s="10"/>
       <x:c r="D721" s="10"/>
+      <x:c r="H721" s="11"/>
     </x:row>
     <x:row r="722">
       <x:c r="B722" s="10"/>
       <x:c r="D722" s="10"/>
+      <x:c r="H722" s="11"/>
     </x:row>
     <x:row r="723">
       <x:c r="B723" s="10"/>
       <x:c r="D723" s="10"/>
+      <x:c r="H723" s="11"/>
     </x:row>
     <x:row r="724">
       <x:c r="B724" s="10"/>
       <x:c r="D724" s="10"/>
+      <x:c r="H724" s="11"/>
     </x:row>
     <x:row r="725">
       <x:c r="B725" s="10"/>
       <x:c r="D725" s="10"/>
+      <x:c r="H725" s="11"/>
     </x:row>
     <x:row r="726">
       <x:c r="B726" s="10"/>
       <x:c r="D726" s="10"/>
+      <x:c r="H726" s="11"/>
     </x:row>
     <x:row r="727">
       <x:c r="B727" s="10"/>
       <x:c r="D727" s="10"/>
+      <x:c r="H727" s="11"/>
     </x:row>
     <x:row r="728">
       <x:c r="B728" s="10"/>
       <x:c r="D728" s="10"/>
+      <x:c r="H728" s="11"/>
     </x:row>
     <x:row r="729">
       <x:c r="B729" s="10"/>
       <x:c r="D729" s="10"/>
+      <x:c r="H729" s="11"/>
     </x:row>
     <x:row r="730">
       <x:c r="B730" s="10"/>
       <x:c r="D730" s="10"/>
+      <x:c r="H730" s="11"/>
     </x:row>
     <x:row r="731">
       <x:c r="B731" s="10"/>
       <x:c r="D731" s="10"/>
+      <x:c r="H731" s="11"/>
     </x:row>
     <x:row r="732">
       <x:c r="B732" s="10"/>
       <x:c r="D732" s="10"/>
+      <x:c r="H732" s="11"/>
     </x:row>
     <x:row r="733">
       <x:c r="B733" s="10"/>
       <x:c r="D733" s="10"/>
+      <x:c r="H733" s="11"/>
     </x:row>
     <x:row r="734">
       <x:c r="B734" s="10"/>
       <x:c r="D734" s="10"/>
+      <x:c r="H734" s="11"/>
     </x:row>
     <x:row r="735">
       <x:c r="B735" s="10"/>
       <x:c r="D735" s="10"/>
+      <x:c r="H735" s="11"/>
     </x:row>
     <x:row r="736">
       <x:c r="B736" s="10"/>
       <x:c r="D736" s="10"/>
+      <x:c r="H736" s="11"/>
     </x:row>
     <x:row r="737">
       <x:c r="B737" s="10"/>
       <x:c r="D737" s="10"/>
+      <x:c r="H737" s="11"/>
     </x:row>
     <x:row r="738">
       <x:c r="B738" s="10"/>
       <x:c r="D738" s="10"/>
+      <x:c r="H738" s="11"/>
     </x:row>
     <x:row r="739">
       <x:c r="B739" s="10"/>
       <x:c r="D739" s="10"/>
+      <x:c r="H739" s="11"/>
     </x:row>
     <x:row r="740">
       <x:c r="B740" s="10"/>
       <x:c r="D740" s="10"/>
+      <x:c r="H740" s="11"/>
     </x:row>
     <x:row r="741">
       <x:c r="B741" s="10"/>
       <x:c r="D741" s="10"/>
+      <x:c r="H741" s="11"/>
     </x:row>
     <x:row r="742">
       <x:c r="B742" s="10"/>
       <x:c r="D742" s="10"/>
+      <x:c r="H742" s="11"/>
     </x:row>
     <x:row r="743">
       <x:c r="B743" s="10"/>
       <x:c r="D743" s="10"/>
+      <x:c r="H743" s="11"/>
     </x:row>
     <x:row r="744">
       <x:c r="B744" s="10"/>
       <x:c r="D744" s="10"/>
+      <x:c r="H744" s="11"/>
     </x:row>
     <x:row r="745">
       <x:c r="B745" s="10"/>
       <x:c r="D745" s="10"/>
+      <x:c r="H745" s="11"/>
     </x:row>
     <x:row r="746">
       <x:c r="B746" s="10"/>
       <x:c r="D746" s="10"/>
+      <x:c r="H746" s="11"/>
     </x:row>
     <x:row r="747">
       <x:c r="B747" s="10"/>
       <x:c r="D747" s="10"/>
+      <x:c r="H747" s="11"/>
     </x:row>
     <x:row r="748">
       <x:c r="B748" s="10"/>
       <x:c r="D748" s="10"/>
+      <x:c r="H748" s="11"/>
     </x:row>
     <x:row r="749">
       <x:c r="B749" s="10"/>
       <x:c r="D749" s="10"/>
+      <x:c r="H749" s="11"/>
     </x:row>
     <x:row r="750">
       <x:c r="B750" s="10"/>
       <x:c r="D750" s="10"/>
+      <x:c r="H750" s="11"/>
     </x:row>
     <x:row r="751">
       <x:c r="B751" s="10"/>
       <x:c r="D751" s="10"/>
+      <x:c r="H751" s="11"/>
     </x:row>
     <x:row r="752">
       <x:c r="B752" s="10"/>
       <x:c r="D752" s="10"/>
+      <x:c r="H752" s="11"/>
     </x:row>
     <x:row r="753">
       <x:c r="B753" s="10"/>
       <x:c r="D753" s="10"/>
+      <x:c r="H753" s="11"/>
     </x:row>
     <x:row r="754">
       <x:c r="B754" s="10"/>
       <x:c r="D754" s="10"/>
+      <x:c r="H754" s="11"/>
     </x:row>
     <x:row r="755">
       <x:c r="B755" s="10"/>
       <x:c r="D755" s="10"/>
+      <x:c r="H755" s="11"/>
     </x:row>
     <x:row r="756">
       <x:c r="B756" s="10"/>
       <x:c r="D756" s="10"/>
+      <x:c r="H756" s="11"/>
     </x:row>
     <x:row r="757">
       <x:c r="B757" s="10"/>
       <x:c r="D757" s="10"/>
+      <x:c r="H757" s="11"/>
     </x:row>
     <x:row r="758">
       <x:c r="B758" s="10"/>
       <x:c r="D758" s="10"/>
+      <x:c r="H758" s="11"/>
     </x:row>
     <x:row r="759">
       <x:c r="B759" s="10"/>
       <x:c r="D759" s="10"/>
+      <x:c r="H759" s="11"/>
     </x:row>
     <x:row r="760">
       <x:c r="B760" s="10"/>
       <x:c r="D760" s="10"/>
+      <x:c r="H760" s="11"/>
     </x:row>
     <x:row r="761">
       <x:c r="B761" s="10"/>
       <x:c r="D761" s="10"/>
+      <x:c r="H761" s="11"/>
     </x:row>
     <x:row r="762">
       <x:c r="B762" s="10"/>
       <x:c r="D762" s="10"/>
+      <x:c r="H762" s="11"/>
     </x:row>
     <x:row r="763">
       <x:c r="B763" s="10"/>
       <x:c r="D763" s="10"/>
+      <x:c r="H763" s="11"/>
     </x:row>
     <x:row r="764">
       <x:c r="B764" s="10"/>
       <x:c r="D764" s="10"/>
+      <x:c r="H764" s="11"/>
     </x:row>
     <x:row r="765">
       <x:c r="B765" s="10"/>
       <x:c r="D765" s="10"/>
+      <x:c r="H765" s="11"/>
     </x:row>
     <x:row r="766">
       <x:c r="B766" s="10"/>
       <x:c r="D766" s="10"/>
+      <x:c r="H766" s="11"/>
     </x:row>
     <x:row r="767">
       <x:c r="B767" s="10"/>
       <x:c r="D767" s="10"/>
+      <x:c r="H767" s="11"/>
     </x:row>
     <x:row r="768">
       <x:c r="B768" s="10"/>
       <x:c r="D768" s="10"/>
+      <x:c r="H768" s="11"/>
     </x:row>
     <x:row r="769">
       <x:c r="B769" s="10"/>
       <x:c r="D769" s="10"/>
+      <x:c r="H769" s="11"/>
     </x:row>
     <x:row r="770">
       <x:c r="B770" s="10"/>
       <x:c r="D770" s="10"/>
+      <x:c r="H770" s="11"/>
     </x:row>
     <x:row r="771">
       <x:c r="B771" s="10"/>
       <x:c r="D771" s="10"/>
+      <x:c r="H771" s="11"/>
     </x:row>
     <x:row r="772">
       <x:c r="B772" s="10"/>
       <x:c r="D772" s="10"/>
+      <x:c r="H772" s="11"/>
     </x:row>
     <x:row r="773">
       <x:c r="B773" s="10"/>
       <x:c r="D773" s="10"/>
+      <x:c r="H773" s="11"/>
     </x:row>
     <x:row r="774">
       <x:c r="B774" s="10"/>
       <x:c r="D774" s="10"/>
+      <x:c r="H774" s="11"/>
     </x:row>
     <x:row r="775">
       <x:c r="B775" s="10"/>
       <x:c r="D775" s="10"/>
+      <x:c r="H775" s="11"/>
     </x:row>
     <x:row r="776">
       <x:c r="B776" s="10"/>
       <x:c r="D776" s="10"/>
+      <x:c r="H776" s="11"/>
     </x:row>
     <x:row r="777">
       <x:c r="B777" s="10"/>
       <x:c r="D777" s="10"/>
+      <x:c r="H777" s="11"/>
     </x:row>
     <x:row r="778">
       <x:c r="B778" s="10"/>
       <x:c r="D778" s="10"/>
+      <x:c r="H778" s="11"/>
     </x:row>
     <x:row r="779">
       <x:c r="B779" s="10"/>
       <x:c r="D779" s="10"/>
+      <x:c r="H779" s="11"/>
     </x:row>
     <x:row r="780">
       <x:c r="B780" s="10"/>
       <x:c r="D780" s="10"/>
+      <x:c r="H780" s="11"/>
     </x:row>
     <x:row r="781">
       <x:c r="B781" s="10"/>
       <x:c r="D781" s="10"/>
+      <x:c r="H781" s="11"/>
     </x:row>
     <x:row r="782">
       <x:c r="B782" s="10"/>
       <x:c r="D782" s="10"/>
+      <x:c r="H782" s="11"/>
     </x:row>
     <x:row r="783">
       <x:c r="B783" s="10"/>
       <x:c r="D783" s="10"/>
+      <x:c r="H783" s="11"/>
     </x:row>
     <x:row r="784">
       <x:c r="B784" s="10"/>
       <x:c r="D784" s="10"/>
+      <x:c r="H784" s="11"/>
     </x:row>
     <x:row r="785">
       <x:c r="B785" s="10"/>
       <x:c r="D785" s="10"/>
+      <x:c r="H785" s="11"/>
     </x:row>
     <x:row r="786">
       <x:c r="B786" s="10"/>
       <x:c r="D786" s="10"/>
+      <x:c r="H786" s="11"/>
     </x:row>
     <x:row r="787">
       <x:c r="B787" s="10"/>
       <x:c r="D787" s="10"/>
+      <x:c r="H787" s="11"/>
     </x:row>
     <x:row r="788">
       <x:c r="B788" s="10"/>
       <x:c r="D788" s="10"/>
+      <x:c r="H788" s="11"/>
     </x:row>
     <x:row r="789">
       <x:c r="B789" s="10"/>
       <x:c r="D789" s="10"/>
+      <x:c r="H789" s="11"/>
     </x:row>
     <x:row r="790">
       <x:c r="B790" s="10"/>
       <x:c r="D790" s="10"/>
+      <x:c r="H790" s="11"/>
     </x:row>
     <x:row r="791">
       <x:c r="B791" s="10"/>
       <x:c r="D791" s="10"/>
+      <x:c r="H791" s="11"/>
     </x:row>
     <x:row r="792">
       <x:c r="B792" s="10"/>
       <x:c r="D792" s="10"/>
+      <x:c r="H792" s="11"/>
     </x:row>
     <x:row r="793">
       <x:c r="B793" s="10"/>
       <x:c r="D793" s="10"/>
+      <x:c r="H793" s="11"/>
     </x:row>
     <x:row r="794">
       <x:c r="B794" s="10"/>
       <x:c r="D794" s="10"/>
+      <x:c r="H794" s="11"/>
     </x:row>
     <x:row r="795">
       <x:c r="B795" s="10"/>
       <x:c r="D795" s="10"/>
+      <x:c r="H795" s="11"/>
     </x:row>
     <x:row r="796">
       <x:c r="B796" s="10"/>
       <x:c r="D796" s="10"/>
+      <x:c r="H796" s="11"/>
     </x:row>
     <x:row r="797">
       <x:c r="B797" s="10"/>
       <x:c r="D797" s="10"/>
+      <x:c r="H797" s="11"/>
     </x:row>
     <x:row r="798">
       <x:c r="B798" s="10"/>
       <x:c r="D798" s="10"/>
+      <x:c r="H798" s="11"/>
     </x:row>
     <x:row r="799">
       <x:c r="B799" s="10"/>
       <x:c r="D799" s="10"/>
+      <x:c r="H799" s="11"/>
     </x:row>
     <x:row r="800">
       <x:c r="B800" s="10"/>
       <x:c r="D800" s="10"/>
+      <x:c r="H800" s="11"/>
     </x:row>
     <x:row r="801">
       <x:c r="B801" s="10"/>
       <x:c r="D801" s="10"/>
+      <x:c r="H801" s="11"/>
     </x:row>
     <x:row r="802">
       <x:c r="B802" s="10"/>
       <x:c r="D802" s="10"/>
+      <x:c r="H802" s="11"/>
     </x:row>
     <x:row r="803">
       <x:c r="B803" s="10"/>
       <x:c r="D803" s="10"/>
+      <x:c r="H803" s="11"/>
     </x:row>
     <x:row r="804">
       <x:c r="B804" s="10"/>
       <x:c r="D804" s="10"/>
+      <x:c r="H804" s="11"/>
     </x:row>
     <x:row r="805">
       <x:c r="B805" s="10"/>
       <x:c r="D805" s="10"/>
+      <x:c r="H805" s="11"/>
     </x:row>
     <x:row r="806">
       <x:c r="B806" s="10"/>
       <x:c r="D806" s="10"/>
+      <x:c r="H806" s="11"/>
     </x:row>
     <x:row r="807">
       <x:c r="B807" s="10"/>
       <x:c r="D807" s="10"/>
+      <x:c r="H807" s="11"/>
     </x:row>
     <x:row r="808">
       <x:c r="B808" s="10"/>
       <x:c r="D808" s="10"/>
+      <x:c r="H808" s="11"/>
     </x:row>
     <x:row r="809">
       <x:c r="B809" s="10"/>
       <x:c r="D809" s="10"/>
+      <x:c r="H809" s="11"/>
     </x:row>
     <x:row r="810">
       <x:c r="B810" s="10"/>
       <x:c r="D810" s="10"/>
+      <x:c r="H810" s="11"/>
     </x:row>
     <x:row r="811">
       <x:c r="B811" s="10"/>
       <x:c r="D811" s="10"/>
+      <x:c r="H811" s="11"/>
     </x:row>
     <x:row r="812">
       <x:c r="B812" s="10"/>
       <x:c r="D812" s="10"/>
+      <x:c r="H812" s="11"/>
     </x:row>
     <x:row r="813">
       <x:c r="B813" s="10"/>
       <x:c r="D813" s="10"/>
+      <x:c r="H813" s="11"/>
     </x:row>
     <x:row r="814">
       <x:c r="B814" s="10"/>
       <x:c r="D814" s="10"/>
+      <x:c r="H814" s="11"/>
     </x:row>
     <x:row r="815">
       <x:c r="B815" s="10"/>
       <x:c r="D815" s="10"/>
+      <x:c r="H815" s="11"/>
     </x:row>
     <x:row r="816">
       <x:c r="B816" s="10"/>
       <x:c r="D816" s="10"/>
+      <x:c r="H816" s="11"/>
     </x:row>
     <x:row r="817">
       <x:c r="B817" s="10"/>
       <x:c r="D817" s="10"/>
+      <x:c r="H817" s="11"/>
     </x:row>
     <x:row r="818">
       <x:c r="B818" s="10"/>
       <x:c r="D818" s="10"/>
+      <x:c r="H818" s="11"/>
     </x:row>
     <x:row r="819">
       <x:c r="B819" s="10"/>
       <x:c r="D819" s="10"/>
+      <x:c r="H819" s="11"/>
     </x:row>
     <x:row r="820">
       <x:c r="B820" s="10"/>
       <x:c r="D820" s="10"/>
+      <x:c r="H820" s="11"/>
     </x:row>
     <x:row r="821">
       <x:c r="B821" s="10"/>
       <x:c r="D821" s="10"/>
+      <x:c r="H821" s="11"/>
     </x:row>
     <x:row r="822">
       <x:c r="B822" s="10"/>
       <x:c r="D822" s="10"/>
+      <x:c r="H822" s="11"/>
     </x:row>
     <x:row r="823">
       <x:c r="B823" s="10"/>
       <x:c r="D823" s="10"/>
+      <x:c r="H823" s="11"/>
     </x:row>
     <x:row r="824">
       <x:c r="B824" s="10"/>
       <x:c r="D824" s="10"/>
+      <x:c r="H824" s="11"/>
     </x:row>
     <x:row r="825">
       <x:c r="B825" s="10"/>
       <x:c r="D825" s="10"/>
+      <x:c r="H825" s="11"/>
     </x:row>
     <x:row r="826">
       <x:c r="B826" s="10"/>
       <x:c r="D826" s="10"/>
+      <x:c r="H826" s="11"/>
     </x:row>
     <x:row r="827">
       <x:c r="B827" s="10"/>
       <x:c r="D827" s="10"/>
+      <x:c r="H827" s="11"/>
     </x:row>
     <x:row r="828">
       <x:c r="B828" s="10"/>
       <x:c r="D828" s="10"/>
+      <x:c r="H828" s="11"/>
     </x:row>
     <x:row r="829">
       <x:c r="B829" s="10"/>
       <x:c r="D829" s="10"/>
+      <x:c r="H829" s="11"/>
     </x:row>
     <x:row r="830">
       <x:c r="B830" s="10"/>
       <x:c r="D830" s="10"/>
+      <x:c r="H830" s="11"/>
     </x:row>
     <x:row r="831">
       <x:c r="B831" s="10"/>
       <x:c r="D831" s="10"/>
+      <x:c r="H831" s="11"/>
     </x:row>
     <x:row r="832">
       <x:c r="B832" s="10"/>
       <x:c r="D832" s="10"/>
+      <x:c r="H832" s="11"/>
     </x:row>
     <x:row r="833">
       <x:c r="B833" s="10"/>
       <x:c r="D833" s="10"/>
+      <x:c r="H833" s="11"/>
     </x:row>
     <x:row r="834">
       <x:c r="B834" s="10"/>
       <x:c r="D834" s="10"/>
+      <x:c r="H834" s="11"/>
     </x:row>
     <x:row r="835">
       <x:c r="B835" s="10"/>
       <x:c r="D835" s="10"/>
+      <x:c r="H835" s="11"/>
     </x:row>
     <x:row r="836">
       <x:c r="B836" s="10"/>
       <x:c r="D836" s="10"/>
+      <x:c r="H836" s="11"/>
     </x:row>
     <x:row r="837">
       <x:c r="B837" s="10"/>
       <x:c r="D837" s="10"/>
+      <x:c r="H837" s="11"/>
     </x:row>
     <x:row r="838">
       <x:c r="B838" s="10"/>
       <x:c r="D838" s="10"/>
+      <x:c r="H838" s="11"/>
     </x:row>
     <x:row r="839">
       <x:c r="B839" s="10"/>
       <x:c r="D839" s="10"/>
+      <x:c r="H839" s="11"/>
     </x:row>
     <x:row r="840">
       <x:c r="B840" s="10"/>
       <x:c r="D840" s="10"/>
+      <x:c r="H840" s="11"/>
     </x:row>
     <x:row r="841">
       <x:c r="B841" s="10"/>
       <x:c r="D841" s="10"/>
+      <x:c r="H841" s="11"/>
     </x:row>
     <x:row r="842">
       <x:c r="B842" s="10"/>
       <x:c r="D842" s="10"/>
+      <x:c r="H842" s="11"/>
     </x:row>
     <x:row r="843">
       <x:c r="B843" s="10"/>
       <x:c r="D843" s="10"/>
+      <x:c r="H843" s="11"/>
     </x:row>
     <x:row r="844">
       <x:c r="B844" s="10"/>
       <x:c r="D844" s="10"/>
+      <x:c r="H844" s="11"/>
     </x:row>
     <x:row r="845">
       <x:c r="B845" s="10"/>
       <x:c r="D845" s="10"/>
+      <x:c r="H845" s="11"/>
     </x:row>
     <x:row r="846">
       <x:c r="B846" s="10"/>
       <x:c r="D846" s="10"/>
+      <x:c r="H846" s="11"/>
     </x:row>
     <x:row r="847">
       <x:c r="B847" s="10"/>
       <x:c r="D847" s="10"/>
+      <x:c r="H847" s="11"/>
     </x:row>
     <x:row r="848">
       <x:c r="B848" s="10"/>
       <x:c r="D848" s="10"/>
+      <x:c r="H848" s="11"/>
     </x:row>
     <x:row r="849">
       <x:c r="B849" s="10"/>
       <x:c r="D849" s="10"/>
+      <x:c r="H849" s="11"/>
     </x:row>
     <x:row r="850">
       <x:c r="B850" s="10"/>
       <x:c r="D850" s="10"/>
+      <x:c r="H850" s="11"/>
     </x:row>
     <x:row r="851">
       <x:c r="B851" s="10"/>
       <x:c r="D851" s="10"/>
+      <x:c r="H851" s="11"/>
     </x:row>
     <x:row r="852">
       <x:c r="B852" s="10"/>
       <x:c r="D852" s="10"/>
+      <x:c r="H852" s="11"/>
     </x:row>
     <x:row r="853">
       <x:c r="B853" s="10"/>
       <x:c r="D853" s="10"/>
+      <x:c r="H853" s="11"/>
     </x:row>
     <x:row r="854">
       <x:c r="B854" s="10"/>
       <x:c r="D854" s="10"/>
+      <x:c r="H854" s="11"/>
     </x:row>
     <x:row r="855">
       <x:c r="B855" s="10"/>
       <x:c r="D855" s="10"/>
+      <x:c r="H855" s="11"/>
     </x:row>
     <x:row r="856">
       <x:c r="B856" s="10"/>
       <x:c r="D856" s="10"/>
+      <x:c r="H856" s="11"/>
     </x:row>
     <x:row r="857">
       <x:c r="B857" s="10"/>
       <x:c r="D857" s="10"/>
+      <x:c r="H857" s="11"/>
     </x:row>
     <x:row r="858">
       <x:c r="B858" s="10"/>
       <x:c r="D858" s="10"/>
+      <x:c r="H858" s="11"/>
     </x:row>
     <x:row r="859">
       <x:c r="B859" s="10"/>
       <x:c r="D859" s="10"/>
+      <x:c r="H859" s="11"/>
     </x:row>
     <x:row r="860">
       <x:c r="B860" s="10"/>
       <x:c r="D860" s="10"/>
+      <x:c r="H860" s="11"/>
     </x:row>
     <x:row r="861">
       <x:c r="B861" s="10"/>
       <x:c r="D861" s="10"/>
+      <x:c r="H861" s="11"/>
     </x:row>
     <x:row r="862">
       <x:c r="B862" s="10"/>
       <x:c r="D862" s="10"/>
+      <x:c r="H862" s="11"/>
     </x:row>
     <x:row r="863">
       <x:c r="B863" s="10"/>
       <x:c r="D863" s="10"/>
+      <x:c r="H863" s="11"/>
     </x:row>
     <x:row r="864">
       <x:c r="B864" s="10"/>
       <x:c r="D864" s="10"/>
+      <x:c r="H864" s="11"/>
     </x:row>
     <x:row r="865">
       <x:c r="B865" s="10"/>
       <x:c r="D865" s="10"/>
+      <x:c r="H865" s="11"/>
     </x:row>
     <x:row r="866">
       <x:c r="B866" s="10"/>
       <x:c r="D866" s="10"/>
+      <x:c r="H866" s="11"/>
     </x:row>
     <x:row r="867">
       <x:c r="B867" s="10"/>
       <x:c r="D867" s="10"/>
+      <x:c r="H867" s="11"/>
     </x:row>
     <x:row r="868">
       <x:c r="B868" s="10"/>
       <x:c r="D868" s="10"/>
+      <x:c r="H868" s="11"/>
     </x:row>
     <x:row r="869">
       <x:c r="B869" s="10"/>
       <x:c r="D869" s="10"/>
+      <x:c r="H869" s="11"/>
     </x:row>
     <x:row r="870">
       <x:c r="B870" s="10"/>
       <x:c r="D870" s="10"/>
+      <x:c r="H870" s="11"/>
     </x:row>
     <x:row r="871">
       <x:c r="B871" s="10"/>
       <x:c r="D871" s="10"/>
+      <x:c r="H871" s="11"/>
     </x:row>
     <x:row r="872">
       <x:c r="B872" s="10"/>
       <x:c r="D872" s="10"/>
+      <x:c r="H872" s="11"/>
     </x:row>
     <x:row r="873">
       <x:c r="B873" s="10"/>
       <x:c r="D873" s="10"/>
+      <x:c r="H873" s="11"/>
     </x:row>
     <x:row r="874">
       <x:c r="B874" s="10"/>
       <x:c r="D874" s="10"/>
+      <x:c r="H874" s="11"/>
     </x:row>
     <x:row r="875">
       <x:c r="B875" s="10"/>
       <x:c r="D875" s="10"/>
+      <x:c r="H875" s="11"/>
     </x:row>
     <x:row r="876">
       <x:c r="B876" s="10"/>
       <x:c r="D876" s="10"/>
+      <x:c r="H876" s="11"/>
     </x:row>
     <x:row r="877">
       <x:c r="B877" s="10"/>
       <x:c r="D877" s="10"/>
+      <x:c r="H877" s="11"/>
     </x:row>
     <x:row r="878">
       <x:c r="B878" s="10"/>
       <x:c r="D878" s="10"/>
+      <x:c r="H878" s="11"/>
     </x:row>
     <x:row r="879">
       <x:c r="B879" s="10"/>
       <x:c r="D879" s="10"/>
+      <x:c r="H879" s="11"/>
     </x:row>
     <x:row r="880">
       <x:c r="B880" s="10"/>
       <x:c r="D880" s="10"/>
+      <x:c r="H880" s="11"/>
     </x:row>
     <x:row r="881">
       <x:c r="B881" s="10"/>
       <x:c r="D881" s="10"/>
+      <x:c r="H881" s="11"/>
     </x:row>
     <x:row r="882">
       <x:c r="B882" s="10"/>
       <x:c r="D882" s="10"/>
+      <x:c r="H882" s="11"/>
     </x:row>
     <x:row r="883">
       <x:c r="B883" s="10"/>
       <x:c r="D883" s="10"/>
+      <x:c r="H883" s="11"/>
     </x:row>
     <x:row r="884">
       <x:c r="B884" s="10"/>
       <x:c r="D884" s="10"/>
+      <x:c r="H884" s="11"/>
     </x:row>
     <x:row r="885">
       <x:c r="B885" s="10"/>
       <x:c r="D885" s="10"/>
+      <x:c r="H885" s="11"/>
     </x:row>
     <x:row r="886">
       <x:c r="B886" s="10"/>
       <x:c r="D886" s="10"/>
+      <x:c r="H886" s="11"/>
     </x:row>
     <x:row r="887">
       <x:c r="B887" s="10"/>
       <x:c r="D887" s="10"/>
+      <x:c r="H887" s="11"/>
     </x:row>
     <x:row r="888">
       <x:c r="B888" s="10"/>
       <x:c r="D888" s="10"/>
+      <x:c r="H888" s="11"/>
     </x:row>
     <x:row r="889">
       <x:c r="B889" s="10"/>
       <x:c r="D889" s="10"/>
+      <x:c r="H889" s="11"/>
     </x:row>
     <x:row r="890">
       <x:c r="B890" s="10"/>
       <x:c r="D890" s="10"/>
+      <x:c r="H890" s="11"/>
     </x:row>
     <x:row r="891">
       <x:c r="B891" s="10"/>
       <x:c r="D891" s="10"/>
+      <x:c r="H891" s="11"/>
     </x:row>
     <x:row r="892">
       <x:c r="B892" s="10"/>
       <x:c r="D892" s="10"/>
+      <x:c r="H892" s="11"/>
     </x:row>
     <x:row r="893">
       <x:c r="B893" s="10"/>
       <x:c r="D893" s="10"/>
+      <x:c r="H893" s="11"/>
     </x:row>
     <x:row r="894">
       <x:c r="B894" s="10"/>
       <x:c r="D894" s="10"/>
+      <x:c r="H894" s="11"/>
     </x:row>
     <x:row r="895">
       <x:c r="B895" s="10"/>
       <x:c r="D895" s="10"/>
+      <x:c r="H895" s="11"/>
     </x:row>
     <x:row r="896">
       <x:c r="B896" s="10"/>
       <x:c r="D896" s="10"/>
+      <x:c r="H896" s="11"/>
     </x:row>
     <x:row r="897">
       <x:c r="B897" s="10"/>
       <x:c r="D897" s="10"/>
+      <x:c r="H897" s="11"/>
     </x:row>
     <x:row r="898">
       <x:c r="B898" s="10"/>
       <x:c r="D898" s="10"/>
+      <x:c r="H898" s="11"/>
     </x:row>
     <x:row r="899">
       <x:c r="B899" s="10"/>
       <x:c r="D899" s="10"/>
+      <x:c r="H899" s="11"/>
     </x:row>
     <x:row r="900">
       <x:c r="B900" s="10"/>
       <x:c r="D900" s="10"/>
+      <x:c r="H900" s="11"/>
     </x:row>
     <x:row r="901">
       <x:c r="B901" s="10"/>
       <x:c r="D901" s="10"/>
+      <x:c r="H901" s="11"/>
     </x:row>
     <x:row r="902">
       <x:c r="B902" s="10"/>
       <x:c r="D902" s="10"/>
+      <x:c r="H902" s="11"/>
     </x:row>
     <x:row r="903">
       <x:c r="B903" s="10"/>
       <x:c r="D903" s="10"/>
+      <x:c r="H903" s="11"/>
     </x:row>
     <x:row r="904">
       <x:c r="B904" s="10"/>
       <x:c r="D904" s="10"/>
+      <x:c r="H904" s="11"/>
     </x:row>
     <x:row r="905">
       <x:c r="B905" s="10"/>
       <x:c r="D905" s="10"/>
+      <x:c r="H905" s="11"/>
     </x:row>
     <x:row r="906">
       <x:c r="B906" s="10"/>
       <x:c r="D906" s="10"/>
+      <x:c r="H906" s="11"/>
     </x:row>
     <x:row r="907">
       <x:c r="B907" s="10"/>
       <x:c r="D907" s="10"/>
+      <x:c r="H907" s="11"/>
     </x:row>
     <x:row r="908">
       <x:c r="B908" s="10"/>
       <x:c r="D908" s="10"/>
+      <x:c r="H908" s="11"/>
     </x:row>
     <x:row r="909">
       <x:c r="B909" s="10"/>
       <x:c r="D909" s="10"/>
+      <x:c r="H909" s="11"/>
     </x:row>
     <x:row r="910">
       <x:c r="B910" s="10"/>
       <x:c r="D910" s="10"/>
+      <x:c r="H910" s="11"/>
     </x:row>
     <x:row r="911">
       <x:c r="B911" s="10"/>
       <x:c r="D911" s="10"/>
+      <x:c r="H911" s="11"/>
     </x:row>
     <x:row r="912">
       <x:c r="B912" s="10"/>
       <x:c r="D912" s="10"/>
+      <x:c r="H912" s="11"/>
     </x:row>
     <x:row r="913">
       <x:c r="B913" s="10"/>
       <x:c r="D913" s="10"/>
+      <x:c r="H913" s="11"/>
     </x:row>
     <x:row r="914">
       <x:c r="B914" s="10"/>
       <x:c r="D914" s="10"/>
+      <x:c r="H914" s="11"/>
     </x:row>
     <x:row r="915">
       <x:c r="B915" s="10"/>
       <x:c r="D915" s="10"/>
+      <x:c r="H915" s="11"/>
     </x:row>
     <x:row r="916">
       <x:c r="B916" s="10"/>
       <x:c r="D916" s="10"/>
+      <x:c r="H916" s="11"/>
     </x:row>
     <x:row r="917">
       <x:c r="B917" s="10"/>
       <x:c r="D917" s="10"/>
+      <x:c r="H917" s="11"/>
     </x:row>
     <x:row r="918">
       <x:c r="B918" s="10"/>
       <x:c r="D918" s="10"/>
+      <x:c r="H918" s="11"/>
     </x:row>
     <x:row r="919">
       <x:c r="B919" s="10"/>
       <x:c r="D919" s="10"/>
+      <x:c r="H919" s="11"/>
     </x:row>
     <x:row r="920">
       <x:c r="B920" s="10"/>
       <x:c r="D920" s="10"/>
+      <x:c r="H920" s="11"/>
     </x:row>
     <x:row r="921">
       <x:c r="B921" s="10"/>
       <x:c r="D921" s="10"/>
+      <x:c r="H921" s="11"/>
     </x:row>
     <x:row r="922">
       <x:c r="B922" s="10"/>
       <x:c r="D922" s="10"/>
+      <x:c r="H922" s="11"/>
     </x:row>
     <x:row r="923">
       <x:c r="B923" s="10"/>
       <x:c r="D923" s="10"/>
+      <x:c r="H923" s="11"/>
     </x:row>
     <x:row r="924">
       <x:c r="B924" s="10"/>
       <x:c r="D924" s="10"/>
+      <x:c r="H924" s="11"/>
     </x:row>
     <x:row r="925">
       <x:c r="B925" s="10"/>
       <x:c r="D925" s="10"/>
+      <x:c r="H925" s="11"/>
     </x:row>
     <x:row r="926">
       <x:c r="B926" s="10"/>
       <x:c r="D926" s="10"/>
+      <x:c r="H926" s="11"/>
     </x:row>
     <x:row r="927">
       <x:c r="B927" s="10"/>
       <x:c r="D927" s="10"/>
+      <x:c r="H927" s="11"/>
     </x:row>
     <x:row r="928">
       <x:c r="B928" s="10"/>
       <x:c r="D928" s="10"/>
+      <x:c r="H928" s="11"/>
     </x:row>
     <x:row r="929">
       <x:c r="B929" s="10"/>
       <x:c r="D929" s="10"/>
+      <x:c r="H929" s="11"/>
     </x:row>
     <x:row r="930">
       <x:c r="B930" s="10"/>
       <x:c r="D930" s="10"/>
+      <x:c r="H930" s="11"/>
     </x:row>
     <x:row r="931">
       <x:c r="B931" s="10"/>
       <x:c r="D931" s="10"/>
+      <x:c r="H931" s="11"/>
     </x:row>
     <x:row r="932">
       <x:c r="B932" s="10"/>
       <x:c r="D932" s="10"/>
+      <x:c r="H932" s="11"/>
     </x:row>
     <x:row r="933">
       <x:c r="B933" s="10"/>
       <x:c r="D933" s="10"/>
+      <x:c r="H933" s="11"/>
     </x:row>
     <x:row r="934">
       <x:c r="B934" s="10"/>
       <x:c r="D934" s="10"/>
+      <x:c r="H934" s="11"/>
     </x:row>
     <x:row r="935">
       <x:c r="B935" s="10"/>
       <x:c r="D935" s="10"/>
+      <x:c r="H935" s="11"/>
     </x:row>
     <x:row r="936">
       <x:c r="B936" s="10"/>
       <x:c r="D936" s="10"/>
+      <x:c r="H936" s="11"/>
     </x:row>
     <x:row r="937">
       <x:c r="B937" s="10"/>
       <x:c r="D937" s="10"/>
+      <x:c r="H937" s="11"/>
     </x:row>
     <x:row r="938">
       <x:c r="B938" s="10"/>
       <x:c r="D938" s="10"/>
+      <x:c r="H938" s="11"/>
     </x:row>
     <x:row r="939">
       <x:c r="B939" s="10"/>
       <x:c r="D939" s="10"/>
+      <x:c r="H939" s="11"/>
     </x:row>
     <x:row r="940">
       <x:c r="B940" s="10"/>
       <x:c r="D940" s="10"/>
+      <x:c r="H940" s="11"/>
     </x:row>
     <x:row r="941">
       <x:c r="B941" s="10"/>
       <x:c r="D941" s="10"/>
+      <x:c r="H941" s="11"/>
     </x:row>
     <x:row r="942">
       <x:c r="B942" s="10"/>
       <x:c r="D942" s="10"/>
+      <x:c r="H942" s="11"/>
     </x:row>
     <x:row r="943">
       <x:c r="B943" s="10"/>
       <x:c r="D943" s="10"/>
+      <x:c r="H943" s="11"/>
     </x:row>
     <x:row r="944">
       <x:c r="B944" s="10"/>
       <x:c r="D944" s="10"/>
+      <x:c r="H944" s="11"/>
     </x:row>
     <x:row r="945">
       <x:c r="B945" s="10"/>
       <x:c r="D945" s="10"/>
+      <x:c r="H945" s="11"/>
     </x:row>
     <x:row r="946">
       <x:c r="B946" s="10"/>
       <x:c r="D946" s="10"/>
+      <x:c r="H946" s="11"/>
     </x:row>
     <x:row r="947">
       <x:c r="B947" s="10"/>
       <x:c r="D947" s="10"/>
+      <x:c r="H947" s="11"/>
     </x:row>
     <x:row r="948">
       <x:c r="B948" s="10"/>
       <x:c r="D948" s="10"/>
+      <x:c r="H948" s="11"/>
     </x:row>
     <x:row r="949">
       <x:c r="B949" s="10"/>
       <x:c r="D949" s="10"/>
+      <x:c r="H949" s="11"/>
     </x:row>
     <x:row r="950">
       <x:c r="B950" s="10"/>
       <x:c r="D950" s="10"/>
+      <x:c r="H950" s="11"/>
     </x:row>
     <x:row r="951">
       <x:c r="B951" s="10"/>
       <x:c r="D951" s="10"/>
+      <x:c r="H951" s="11"/>
     </x:row>
     <x:row r="952">
       <x:c r="B952" s="10"/>
       <x:c r="D952" s="10"/>
+      <x:c r="H952" s="11"/>
     </x:row>
     <x:row r="953">
       <x:c r="B953" s="10"/>
       <x:c r="D953" s="10"/>
+      <x:c r="H953" s="11"/>
     </x:row>
     <x:row r="954">
       <x:c r="B954" s="10"/>
       <x:c r="D954" s="10"/>
+      <x:c r="H954" s="11"/>
     </x:row>
     <x:row r="955">
       <x:c r="B955" s="10"/>
       <x:c r="D955" s="10"/>
+      <x:c r="H955" s="11"/>
     </x:row>
     <x:row r="956">
       <x:c r="B956" s="10"/>
       <x:c r="D956" s="10"/>
+      <x:c r="H956" s="11"/>
     </x:row>
     <x:row r="957">
       <x:c r="B957" s="10"/>
       <x:c r="D957" s="10"/>
+      <x:c r="H957" s="11"/>
     </x:row>
     <x:row r="958">
       <x:c r="B958" s="10"/>
       <x:c r="D958" s="10"/>
+      <x:c r="H958" s="11"/>
     </x:row>
     <x:row r="959">
       <x:c r="B959" s="10"/>
       <x:c r="D959" s="10"/>
+      <x:c r="H959" s="11"/>
     </x:row>
     <x:row r="960">
       <x:c r="B960" s="10"/>
       <x:c r="D960" s="10"/>
+      <x:c r="H960" s="11"/>
     </x:row>
     <x:row r="961">
       <x:c r="B961" s="10"/>
       <x:c r="D961" s="10"/>
+      <x:c r="H961" s="11"/>
     </x:row>
     <x:row r="962">
       <x:c r="B962" s="10"/>
       <x:c r="D962" s="10"/>
+      <x:c r="H962" s="11"/>
     </x:row>
     <x:row r="963">
       <x:c r="B963" s="10"/>
       <x:c r="D963" s="10"/>
+      <x:c r="H963" s="11"/>
     </x:row>
     <x:row r="964">
       <x:c r="B964" s="10"/>
       <x:c r="D964" s="10"/>
+      <x:c r="H964" s="11"/>
     </x:row>
     <x:row r="965">
       <x:c r="B965" s="10"/>
       <x:c r="D965" s="10"/>
+      <x:c r="H965" s="11"/>
     </x:row>
     <x:row r="966">
       <x:c r="B966" s="10"/>
       <x:c r="D966" s="10"/>
+      <x:c r="H966" s="11"/>
     </x:row>
     <x:row r="967">
       <x:c r="B967" s="10"/>
       <x:c r="D967" s="10"/>
+      <x:c r="H967" s="11"/>
     </x:row>
     <x:row r="968">
       <x:c r="B968" s="10"/>
       <x:c r="D968" s="10"/>
+      <x:c r="H968" s="11"/>
     </x:row>
     <x:row r="969">
       <x:c r="B969" s="10"/>
       <x:c r="D969" s="10"/>
+      <x:c r="H969" s="11"/>
     </x:row>
     <x:row r="970">
       <x:c r="B970" s="10"/>
       <x:c r="D970" s="10"/>
+      <x:c r="H970" s="11"/>
     </x:row>
     <x:row r="971">
       <x:c r="B971" s="10"/>
       <x:c r="D971" s="10"/>
+      <x:c r="H971" s="11"/>
     </x:row>
     <x:row r="972">
       <x:c r="B972" s="10"/>
       <x:c r="D972" s="10"/>
+      <x:c r="H972" s="11"/>
     </x:row>
     <x:row r="973">
       <x:c r="B973" s="10"/>
       <x:c r="D973" s="10"/>
+      <x:c r="H973" s="11"/>
     </x:row>
     <x:row r="974">
       <x:c r="B974" s="10"/>
       <x:c r="D974" s="10"/>
+      <x:c r="H974" s="11"/>
     </x:row>
     <x:row r="975">
       <x:c r="B975" s="10"/>
       <x:c r="D975" s="10"/>
+      <x:c r="H975" s="11"/>
     </x:row>
     <x:row r="976">
       <x:c r="B976" s="10"/>
       <x:c r="D976" s="10"/>
+      <x:c r="H976" s="11"/>
     </x:row>
     <x:row r="977">
       <x:c r="B977" s="10"/>
       <x:c r="D977" s="10"/>
+      <x:c r="H977" s="11"/>
     </x:row>
     <x:row r="978">
       <x:c r="B978" s="10"/>
       <x:c r="D978" s="10"/>
+      <x:c r="H978" s="11"/>
     </x:row>
     <x:row r="979">
       <x:c r="B979" s="10"/>
       <x:c r="D979" s="10"/>
+      <x:c r="H979" s="11"/>
     </x:row>
     <x:row r="980">
       <x:c r="B980" s="10"/>
       <x:c r="D980" s="10"/>
+      <x:c r="H980" s="11"/>
     </x:row>
     <x:row r="981">
       <x:c r="B981" s="10"/>
       <x:c r="D981" s="10"/>
+      <x:c r="H981" s="11"/>
     </x:row>
     <x:row r="982">
       <x:c r="B982" s="10"/>
       <x:c r="D982" s="10"/>
+      <x:c r="H982" s="11"/>
     </x:row>
     <x:row r="983">
       <x:c r="B983" s="10"/>
       <x:c r="D983" s="10"/>
+      <x:c r="H983" s="11"/>
     </x:row>
     <x:row r="984">
       <x:c r="B984" s="10"/>
       <x:c r="D984" s="10"/>
+      <x:c r="H984" s="11"/>
     </x:row>
     <x:row r="985">
       <x:c r="B985" s="10"/>
       <x:c r="D985" s="10"/>
+      <x:c r="H985" s="11"/>
     </x:row>
     <x:row r="986">
       <x:c r="B986" s="10"/>
       <x:c r="D986" s="10"/>
+      <x:c r="H986" s="11"/>
     </x:row>
     <x:row r="987">
       <x:c r="B987" s="10"/>
       <x:c r="D987" s="10"/>
+      <x:c r="H987" s="11"/>
     </x:row>
     <x:row r="988">
       <x:c r="B988" s="10"/>
       <x:c r="D988" s="10"/>
+      <x:c r="H988" s="11"/>
     </x:row>
     <x:row r="989">
       <x:c r="B989" s="10"/>
       <x:c r="D989" s="10"/>
+      <x:c r="H989" s="11"/>
     </x:row>
     <x:row r="990">
       <x:c r="B990" s="10"/>
       <x:c r="D990" s="10"/>
+      <x:c r="H990" s="11"/>
     </x:row>
     <x:row r="991">
       <x:c r="B991" s="10"/>
       <x:c r="D991" s="10"/>
+      <x:c r="H991" s="11"/>
     </x:row>
     <x:row r="992">
       <x:c r="B992" s="10"/>
       <x:c r="D992" s="10"/>
+      <x:c r="H992" s="11"/>
     </x:row>
     <x:row r="993">
       <x:c r="B993" s="10"/>
       <x:c r="D993" s="10"/>
+      <x:c r="H993" s="11"/>
     </x:row>
     <x:row r="994">
       <x:c r="B994" s="10"/>
       <x:c r="D994" s="10"/>
+      <x:c r="H994" s="11"/>
     </x:row>
     <x:row r="995">
       <x:c r="B995" s="10"/>
       <x:c r="D995" s="10"/>
+      <x:c r="H995" s="11"/>
     </x:row>
     <x:row r="996">
       <x:c r="B996" s="10"/>
       <x:c r="D996" s="10"/>
+      <x:c r="H996" s="11"/>
     </x:row>
     <x:row r="997">
       <x:c r="B997" s="10"/>
       <x:c r="D997" s="10"/>
+      <x:c r="H997" s="11"/>
     </x:row>
     <x:row r="998">
       <x:c r="B998" s="10"/>
       <x:c r="D998" s="10"/>
+      <x:c r="H998" s="11"/>
     </x:row>
     <x:row r="999">
       <x:c r="B999" s="10"/>
       <x:c r="D999" s="10"/>
+      <x:c r="H999" s="11"/>
     </x:row>
     <x:row r="1000">
       <x:c r="B1000" s="10"/>
       <x:c r="D1000" s="10"/>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="8" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="40" customHeight="1">
-      <x:c r="A1" s="8" t="str">
-        <x:v>项目</x:v>
-      </x:c>
-      <x:c r="B1" s="8" t="str">
-        <x:v>说明</x:v>
-      </x:c>
-      <x:c r="C1" s="8" t="str">
-        <x:v>处理建议</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="9" t="str">
-        <x:v>字段路径</x:v>
-      </x:c>
-      <x:c r="B2" s="9" t="str">
-        <x:v>使用中文路径展示，例如：账单信息-期次、文件信息-身份证正面</x:v>
-      </x:c>
-      <x:c r="C2" s="9" t="str">
-        <x:v>业务和测试可直接按中文路径定位模板列</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="9" t="str">
-        <x:v>是否阻断导入</x:v>
-      </x:c>
-      <x:c r="B3" s="9" t="str">
-        <x:v>是：本次订单未生成；否：订单已导入但材料需补齐</x:v>
-      </x:c>
-      <x:c r="C3" s="9" t="str">
-        <x:v>阻断失败修正后重新上传；材料缺失进入补传页处理</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="9" t="str">
-        <x:v>材料项</x:v>
-      </x:c>
-      <x:c r="B4" s="9" t="str">
-        <x:v>仅材料类问题填写</x:v>
-      </x:c>
-      <x:c r="C4" s="9" t="str">
-        <x:v>材料补传页按来源平台、订单编号、客户姓名、业务类型、材料项处理</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="9" t="str">
-        <x:v>续租订单</x:v>
-      </x:c>
-      <x:c r="B5" s="9" t="str">
-        <x:v>续租订单必须关联首租订单，且不能是已完结、已归还、已买断状态</x:v>
-      </x:c>
-      <x:c r="C5" s="9" t="str">
-        <x:v>缺失首租订单或状态不满足时阻断导入</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="9" t="str">
-        <x:v>合同必传项</x:v>
-      </x:c>
-      <x:c r="B6" s="9" t="str">
-        <x:v>新旧合同模式的合同材料按必传材料处理</x:v>
-      </x:c>
-      <x:c r="C6" s="9" t="str">
-        <x:v>缺失时在材料补传页按合同模式补齐</x:v>
+      <x:c r="H1000" s="11"/>
+    </x:row>
+    <x:row r="1001">
+      <x:c r="A1001" t="str">
+        <x:v>创新</x:v>
+      </x:c>
+      <x:c r="B1001" t="str">
+        <x:v>DR202606100001</x:v>
+      </x:c>
+      <x:c r="C1001" t="str">
+        <x:v>创新租赁旧合同批次01</x:v>
+      </x:c>
+      <x:c r="D1001" t="str">
+        <x:v>26012915050167612331</x:v>
+      </x:c>
+      <x:c r="E1001" t="str">
+        <x:v>周强</x:v>
+      </x:c>
+      <x:c r="F1001" t="str">
+        <x:v>租赁</x:v>
+      </x:c>
+      <x:c r="G1001" t="str">
+        <x:v>主订单</x:v>
+      </x:c>
+      <x:c r="H1001" t="n">
+        <x:v>8650</x:v>
+      </x:c>
+      <x:c r="I1001" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J1001" t="str">
+        <x:v>阻断失败</x:v>
+      </x:c>
+      <x:c r="K1001" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L1001" t="str">
+        <x:v>同一批资产已在批次 DR202606080003 导入落库，以第一次导入数据为准，本批次不能重复导入或自动覆盖。</x:v>
+      </x:c>
+      <x:c r="M1001" t="str">
+        <x:v>请到首次导入批次查看该订单；如需更正，按原批次处理或走批量补传/更正流程。</x:v>
+      </x:c>
+      <x:c r="N1001" t="str">
+        <x:v>2026-06-10 20:15:32</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
